--- a/output/version3/test/15-10/MARL/IL/RL-RL (+comm)/(RL+RL) test results.xlsx
+++ b/output/version3/test/15-10/MARL/IL/RL-RL (+comm)/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>607</v>
+        <v>540</v>
       </c>
       <c r="C2" t="n">
-        <v>595</v>
+        <v>567</v>
       </c>
       <c r="D2" t="n">
-        <v>685</v>
+        <v>626</v>
       </c>
       <c r="E2" t="n">
-        <v>567</v>
+        <v>502</v>
       </c>
       <c r="F2" t="n">
-        <v>613</v>
+        <v>696</v>
       </c>
       <c r="G2" t="n">
-        <v>713</v>
+        <v>555</v>
       </c>
       <c r="H2" t="n">
-        <v>572</v>
+        <v>528</v>
       </c>
       <c r="I2" t="n">
-        <v>614</v>
+        <v>646</v>
       </c>
       <c r="J2" t="n">
-        <v>641</v>
+        <v>592</v>
       </c>
       <c r="K2" t="n">
-        <v>601</v>
+        <v>702</v>
       </c>
       <c r="L2" t="n">
-        <v>620.8</v>
+        <v>595.4</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>615</v>
+        <v>598</v>
       </c>
       <c r="C3" t="n">
-        <v>650</v>
+        <v>676</v>
       </c>
       <c r="D3" t="n">
-        <v>650</v>
+        <v>587</v>
       </c>
       <c r="E3" t="n">
-        <v>628</v>
+        <v>597</v>
       </c>
       <c r="F3" t="n">
-        <v>645</v>
+        <v>606</v>
       </c>
       <c r="G3" t="n">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="H3" t="n">
-        <v>705</v>
+        <v>747</v>
       </c>
       <c r="I3" t="n">
-        <v>620</v>
+        <v>593</v>
       </c>
       <c r="J3" t="n">
-        <v>623</v>
+        <v>636</v>
       </c>
       <c r="K3" t="n">
-        <v>613</v>
+        <v>573</v>
       </c>
       <c r="L3" t="n">
-        <v>633.1</v>
+        <v>618.9</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>581</v>
+        <v>530</v>
       </c>
       <c r="C4" t="n">
-        <v>566</v>
+        <v>642</v>
       </c>
       <c r="D4" t="n">
-        <v>649</v>
+        <v>731</v>
       </c>
       <c r="E4" t="n">
-        <v>599</v>
+        <v>672</v>
       </c>
       <c r="F4" t="n">
-        <v>675</v>
+        <v>656</v>
       </c>
       <c r="G4" t="n">
-        <v>721</v>
+        <v>612</v>
       </c>
       <c r="H4" t="n">
-        <v>585</v>
+        <v>710</v>
       </c>
       <c r="I4" t="n">
-        <v>657</v>
+        <v>611</v>
       </c>
       <c r="J4" t="n">
-        <v>751</v>
+        <v>622</v>
       </c>
       <c r="K4" t="n">
-        <v>728</v>
+        <v>686</v>
       </c>
       <c r="L4" t="n">
-        <v>651.2</v>
+        <v>647.2</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>628</v>
+        <v>648</v>
       </c>
       <c r="C5" t="n">
-        <v>715</v>
+        <v>645</v>
       </c>
       <c r="D5" t="n">
-        <v>652</v>
+        <v>698</v>
       </c>
       <c r="E5" t="n">
-        <v>666</v>
+        <v>616</v>
       </c>
       <c r="F5" t="n">
-        <v>634</v>
+        <v>641</v>
       </c>
       <c r="G5" t="n">
-        <v>669</v>
+        <v>602</v>
       </c>
       <c r="H5" t="n">
-        <v>611</v>
+        <v>632</v>
       </c>
       <c r="I5" t="n">
-        <v>747</v>
+        <v>631</v>
       </c>
       <c r="J5" t="n">
-        <v>681</v>
+        <v>689</v>
       </c>
       <c r="K5" t="n">
-        <v>719</v>
+        <v>613</v>
       </c>
       <c r="L5" t="n">
-        <v>672.2</v>
+        <v>641.5</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>538</v>
+        <v>604</v>
       </c>
       <c r="C6" t="n">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="D6" t="n">
-        <v>556</v>
+        <v>637</v>
       </c>
       <c r="E6" t="n">
-        <v>663</v>
+        <v>573</v>
       </c>
       <c r="F6" t="n">
-        <v>682</v>
+        <v>658</v>
       </c>
       <c r="G6" t="n">
-        <v>679</v>
+        <v>533</v>
       </c>
       <c r="H6" t="n">
-        <v>704</v>
+        <v>592</v>
       </c>
       <c r="I6" t="n">
-        <v>578</v>
+        <v>536</v>
       </c>
       <c r="J6" t="n">
+        <v>617</v>
+      </c>
+      <c r="K6" t="n">
         <v>582</v>
       </c>
-      <c r="K6" t="n">
-        <v>630</v>
-      </c>
       <c r="L6" t="n">
-        <v>618.9</v>
+        <v>590.4</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>502</v>
+        <v>756</v>
       </c>
       <c r="C7" t="n">
-        <v>664</v>
+        <v>658</v>
       </c>
       <c r="D7" t="n">
-        <v>604</v>
+        <v>640</v>
       </c>
       <c r="E7" t="n">
-        <v>581</v>
+        <v>653</v>
       </c>
       <c r="F7" t="n">
-        <v>596</v>
+        <v>576</v>
       </c>
       <c r="G7" t="n">
-        <v>770</v>
+        <v>716</v>
       </c>
       <c r="H7" t="n">
-        <v>538</v>
+        <v>570</v>
       </c>
       <c r="I7" t="n">
-        <v>583</v>
+        <v>601</v>
       </c>
       <c r="J7" t="n">
-        <v>603</v>
+        <v>519</v>
       </c>
       <c r="K7" t="n">
-        <v>654</v>
+        <v>487</v>
       </c>
       <c r="L7" t="n">
-        <v>609.5</v>
+        <v>617.6</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>525</v>
+        <v>657</v>
       </c>
       <c r="C8" t="n">
-        <v>592</v>
+        <v>671</v>
       </c>
       <c r="D8" t="n">
-        <v>523</v>
+        <v>559</v>
       </c>
       <c r="E8" t="n">
-        <v>552</v>
+        <v>604</v>
       </c>
       <c r="F8" t="n">
-        <v>632</v>
+        <v>534</v>
       </c>
       <c r="G8" t="n">
-        <v>616</v>
+        <v>537</v>
       </c>
       <c r="H8" t="n">
-        <v>654</v>
+        <v>594</v>
       </c>
       <c r="I8" t="n">
-        <v>528</v>
+        <v>637</v>
       </c>
       <c r="J8" t="n">
-        <v>632</v>
+        <v>641</v>
       </c>
       <c r="K8" t="n">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="L8" t="n">
-        <v>585</v>
+        <v>602.4</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="C9" t="n">
-        <v>592</v>
+        <v>618</v>
       </c>
       <c r="D9" t="n">
-        <v>593</v>
+        <v>536</v>
       </c>
       <c r="E9" t="n">
-        <v>593</v>
+        <v>534</v>
       </c>
       <c r="F9" t="n">
-        <v>637</v>
+        <v>558</v>
       </c>
       <c r="G9" t="n">
-        <v>619</v>
+        <v>550</v>
       </c>
       <c r="H9" t="n">
-        <v>578</v>
+        <v>560</v>
       </c>
       <c r="I9" t="n">
-        <v>615</v>
+        <v>556</v>
       </c>
       <c r="J9" t="n">
-        <v>571</v>
+        <v>652</v>
       </c>
       <c r="K9" t="n">
-        <v>541</v>
+        <v>582</v>
       </c>
       <c r="L9" t="n">
-        <v>596.4</v>
+        <v>576.3</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>668</v>
+        <v>893</v>
       </c>
       <c r="C10" t="n">
-        <v>733</v>
+        <v>645</v>
       </c>
       <c r="D10" t="n">
-        <v>638</v>
+        <v>829</v>
       </c>
       <c r="E10" t="n">
-        <v>782</v>
+        <v>752</v>
       </c>
       <c r="F10" t="n">
-        <v>749</v>
+        <v>714</v>
       </c>
       <c r="G10" t="n">
-        <v>660</v>
+        <v>704</v>
       </c>
       <c r="H10" t="n">
-        <v>728</v>
+        <v>628</v>
       </c>
       <c r="I10" t="n">
-        <v>661</v>
+        <v>761</v>
       </c>
       <c r="J10" t="n">
-        <v>669</v>
+        <v>724</v>
       </c>
       <c r="K10" t="n">
-        <v>733</v>
+        <v>779</v>
       </c>
       <c r="L10" t="n">
-        <v>702.1</v>
+        <v>742.9</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>600</v>
+        <v>654</v>
       </c>
       <c r="C11" t="n">
+        <v>604</v>
+      </c>
+      <c r="D11" t="n">
+        <v>744</v>
+      </c>
+      <c r="E11" t="n">
+        <v>661</v>
+      </c>
+      <c r="F11" t="n">
+        <v>658</v>
+      </c>
+      <c r="G11" t="n">
+        <v>573</v>
+      </c>
+      <c r="H11" t="n">
+        <v>681</v>
+      </c>
+      <c r="I11" t="n">
         <v>599</v>
       </c>
-      <c r="D11" t="n">
-        <v>646</v>
-      </c>
-      <c r="E11" t="n">
-        <v>728</v>
-      </c>
-      <c r="F11" t="n">
-        <v>634</v>
-      </c>
-      <c r="G11" t="n">
-        <v>657</v>
-      </c>
-      <c r="H11" t="n">
-        <v>638</v>
-      </c>
-      <c r="I11" t="n">
-        <v>623</v>
-      </c>
       <c r="J11" t="n">
-        <v>670</v>
+        <v>591</v>
       </c>
       <c r="K11" t="n">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="L11" t="n">
-        <v>637.4</v>
+        <v>634.6</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>672</v>
+        <v>582</v>
       </c>
       <c r="C12" t="n">
-        <v>743</v>
+        <v>608</v>
       </c>
       <c r="D12" t="n">
-        <v>723</v>
+        <v>619</v>
       </c>
       <c r="E12" t="n">
-        <v>705</v>
+        <v>608</v>
       </c>
       <c r="F12" t="n">
-        <v>614</v>
+        <v>621</v>
       </c>
       <c r="G12" t="n">
-        <v>701</v>
+        <v>636</v>
       </c>
       <c r="H12" t="n">
-        <v>676</v>
+        <v>634</v>
       </c>
       <c r="I12" t="n">
-        <v>669</v>
+        <v>741</v>
       </c>
       <c r="J12" t="n">
-        <v>731</v>
+        <v>637</v>
       </c>
       <c r="K12" t="n">
-        <v>585</v>
+        <v>689</v>
       </c>
       <c r="L12" t="n">
-        <v>681.9</v>
+        <v>637.5</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>811</v>
+        <v>730</v>
       </c>
       <c r="C13" t="n">
-        <v>806</v>
+        <v>705</v>
       </c>
       <c r="D13" t="n">
-        <v>725</v>
+        <v>707</v>
       </c>
       <c r="E13" t="n">
-        <v>641</v>
+        <v>720</v>
       </c>
       <c r="F13" t="n">
-        <v>706</v>
+        <v>749</v>
       </c>
       <c r="G13" t="n">
-        <v>764</v>
+        <v>815</v>
       </c>
       <c r="H13" t="n">
-        <v>659</v>
+        <v>762</v>
       </c>
       <c r="I13" t="n">
-        <v>799</v>
+        <v>748</v>
       </c>
       <c r="J13" t="n">
-        <v>784</v>
+        <v>731</v>
       </c>
       <c r="K13" t="n">
-        <v>783</v>
+        <v>777</v>
       </c>
       <c r="L13" t="n">
-        <v>747.8</v>
+        <v>744.4</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>658</v>
+        <v>777</v>
       </c>
       <c r="C14" t="n">
-        <v>869</v>
+        <v>569</v>
       </c>
       <c r="D14" t="n">
-        <v>676</v>
+        <v>761</v>
       </c>
       <c r="E14" t="n">
-        <v>731</v>
+        <v>623</v>
       </c>
       <c r="F14" t="n">
-        <v>644</v>
+        <v>761</v>
       </c>
       <c r="G14" t="n">
-        <v>658</v>
+        <v>695</v>
       </c>
       <c r="H14" t="n">
-        <v>745</v>
+        <v>637</v>
       </c>
       <c r="I14" t="n">
-        <v>714</v>
+        <v>630</v>
       </c>
       <c r="J14" t="n">
-        <v>627</v>
+        <v>665</v>
       </c>
       <c r="K14" t="n">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="L14" t="n">
-        <v>704.4</v>
+        <v>683.6</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>715</v>
+        <v>628</v>
       </c>
       <c r="C15" t="n">
-        <v>659</v>
+        <v>754</v>
       </c>
       <c r="D15" t="n">
-        <v>691</v>
+        <v>646</v>
       </c>
       <c r="E15" t="n">
-        <v>684</v>
+        <v>699</v>
       </c>
       <c r="F15" t="n">
-        <v>647</v>
+        <v>656</v>
       </c>
       <c r="G15" t="n">
-        <v>691</v>
+        <v>665</v>
       </c>
       <c r="H15" t="n">
-        <v>689</v>
+        <v>735</v>
       </c>
       <c r="I15" t="n">
-        <v>678</v>
+        <v>660</v>
       </c>
       <c r="J15" t="n">
-        <v>686</v>
+        <v>706</v>
       </c>
       <c r="K15" t="n">
-        <v>724</v>
+        <v>658</v>
       </c>
       <c r="L15" t="n">
-        <v>686.4</v>
+        <v>680.7</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>670</v>
+        <v>727</v>
       </c>
       <c r="C16" t="n">
-        <v>600</v>
+        <v>628</v>
       </c>
       <c r="D16" t="n">
-        <v>665</v>
+        <v>632</v>
       </c>
       <c r="E16" t="n">
-        <v>566</v>
+        <v>784</v>
       </c>
       <c r="F16" t="n">
-        <v>802</v>
+        <v>562</v>
       </c>
       <c r="G16" t="n">
-        <v>647</v>
+        <v>694</v>
       </c>
       <c r="H16" t="n">
-        <v>730</v>
+        <v>631</v>
       </c>
       <c r="I16" t="n">
-        <v>762</v>
+        <v>599</v>
       </c>
       <c r="J16" t="n">
-        <v>744</v>
+        <v>692</v>
       </c>
       <c r="K16" t="n">
-        <v>706</v>
+        <v>614</v>
       </c>
       <c r="L16" t="n">
-        <v>689.2</v>
+        <v>656.3</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>616</v>
+        <v>644</v>
       </c>
       <c r="C17" t="n">
-        <v>521</v>
+        <v>599</v>
       </c>
       <c r="D17" t="n">
-        <v>549</v>
+        <v>748</v>
       </c>
       <c r="E17" t="n">
-        <v>689</v>
+        <v>565</v>
       </c>
       <c r="F17" t="n">
-        <v>695</v>
+        <v>732</v>
       </c>
       <c r="G17" t="n">
-        <v>716</v>
+        <v>640</v>
       </c>
       <c r="H17" t="n">
-        <v>567</v>
+        <v>597</v>
       </c>
       <c r="I17" t="n">
-        <v>627</v>
+        <v>591</v>
       </c>
       <c r="J17" t="n">
-        <v>678</v>
+        <v>686</v>
       </c>
       <c r="K17" t="n">
-        <v>603</v>
+        <v>553</v>
       </c>
       <c r="L17" t="n">
-        <v>626.1</v>
+        <v>635.5</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>746</v>
+        <v>664</v>
       </c>
       <c r="C18" t="n">
-        <v>642</v>
+        <v>629</v>
       </c>
       <c r="D18" t="n">
-        <v>643</v>
+        <v>637</v>
       </c>
       <c r="E18" t="n">
-        <v>728</v>
+        <v>644</v>
       </c>
       <c r="F18" t="n">
-        <v>706</v>
+        <v>691</v>
       </c>
       <c r="G18" t="n">
-        <v>686</v>
+        <v>673</v>
       </c>
       <c r="H18" t="n">
-        <v>681</v>
+        <v>606</v>
       </c>
       <c r="I18" t="n">
-        <v>564</v>
+        <v>605</v>
       </c>
       <c r="J18" t="n">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="K18" t="n">
-        <v>673</v>
+        <v>684</v>
       </c>
       <c r="L18" t="n">
-        <v>677.2</v>
+        <v>653.7</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>832</v>
+        <v>624</v>
       </c>
       <c r="C19" t="n">
-        <v>829</v>
+        <v>768</v>
       </c>
       <c r="D19" t="n">
-        <v>559</v>
+        <v>780</v>
       </c>
       <c r="E19" t="n">
-        <v>623</v>
+        <v>670</v>
       </c>
       <c r="F19" t="n">
-        <v>841</v>
+        <v>750</v>
       </c>
       <c r="G19" t="n">
-        <v>591</v>
+        <v>784</v>
       </c>
       <c r="H19" t="n">
-        <v>750</v>
+        <v>643</v>
       </c>
       <c r="I19" t="n">
-        <v>681</v>
+        <v>648</v>
       </c>
       <c r="J19" t="n">
-        <v>767</v>
+        <v>612</v>
       </c>
       <c r="K19" t="n">
-        <v>771</v>
+        <v>695</v>
       </c>
       <c r="L19" t="n">
-        <v>724.4</v>
+        <v>697.4</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>693</v>
+        <v>752</v>
       </c>
       <c r="C20" t="n">
-        <v>744</v>
+        <v>727</v>
       </c>
       <c r="D20" t="n">
+        <v>791</v>
+      </c>
+      <c r="E20" t="n">
+        <v>691</v>
+      </c>
+      <c r="F20" t="n">
+        <v>700</v>
+      </c>
+      <c r="G20" t="n">
         <v>849</v>
       </c>
-      <c r="E20" t="n">
-        <v>660</v>
-      </c>
-      <c r="F20" t="n">
-        <v>758</v>
-      </c>
-      <c r="G20" t="n">
-        <v>630</v>
-      </c>
       <c r="H20" t="n">
-        <v>716</v>
+        <v>688</v>
       </c>
       <c r="I20" t="n">
-        <v>792</v>
+        <v>701</v>
       </c>
       <c r="J20" t="n">
-        <v>686</v>
+        <v>719</v>
       </c>
       <c r="K20" t="n">
-        <v>675</v>
+        <v>788</v>
       </c>
       <c r="L20" t="n">
-        <v>720.3</v>
+        <v>740.6</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>780</v>
+        <v>668</v>
       </c>
       <c r="C21" t="n">
-        <v>680</v>
+        <v>760</v>
       </c>
       <c r="D21" t="n">
-        <v>659</v>
+        <v>648</v>
       </c>
       <c r="E21" t="n">
-        <v>683</v>
+        <v>636</v>
       </c>
       <c r="F21" t="n">
-        <v>642</v>
+        <v>630</v>
       </c>
       <c r="G21" t="n">
-        <v>638</v>
+        <v>710</v>
       </c>
       <c r="H21" t="n">
-        <v>625</v>
+        <v>698</v>
       </c>
       <c r="I21" t="n">
-        <v>564</v>
+        <v>748</v>
       </c>
       <c r="J21" t="n">
-        <v>705</v>
+        <v>764</v>
       </c>
       <c r="K21" t="n">
-        <v>715</v>
+        <v>619</v>
       </c>
       <c r="L21" t="n">
-        <v>669.1</v>
+        <v>688.1</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>587</v>
+        <v>744</v>
       </c>
       <c r="C22" t="n">
-        <v>663</v>
+        <v>548</v>
       </c>
       <c r="D22" t="n">
-        <v>610</v>
+        <v>646</v>
       </c>
       <c r="E22" t="n">
-        <v>643</v>
+        <v>584</v>
       </c>
       <c r="F22" t="n">
-        <v>775</v>
+        <v>567</v>
       </c>
       <c r="G22" t="n">
-        <v>658</v>
+        <v>701</v>
       </c>
       <c r="H22" t="n">
+        <v>612</v>
+      </c>
+      <c r="I22" t="n">
+        <v>649</v>
+      </c>
+      <c r="J22" t="n">
         <v>666</v>
       </c>
-      <c r="I22" t="n">
-        <v>633</v>
-      </c>
-      <c r="J22" t="n">
-        <v>586</v>
-      </c>
       <c r="K22" t="n">
-        <v>632</v>
+        <v>625</v>
       </c>
       <c r="L22" t="n">
-        <v>645.3</v>
+        <v>634.2</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>682</v>
+        <v>569</v>
       </c>
       <c r="C23" t="n">
-        <v>723</v>
+        <v>582</v>
       </c>
       <c r="D23" t="n">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="E23" t="n">
-        <v>646</v>
+        <v>598</v>
       </c>
       <c r="F23" t="n">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="G23" t="n">
-        <v>593</v>
+        <v>648</v>
       </c>
       <c r="H23" t="n">
-        <v>662</v>
+        <v>649</v>
       </c>
       <c r="I23" t="n">
-        <v>651</v>
+        <v>599</v>
       </c>
       <c r="J23" t="n">
-        <v>714</v>
+        <v>703</v>
       </c>
       <c r="K23" t="n">
-        <v>594</v>
+        <v>713</v>
       </c>
       <c r="L23" t="n">
-        <v>640.1</v>
+        <v>620.9</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>775</v>
+        <v>651</v>
       </c>
       <c r="C24" t="n">
-        <v>641</v>
+        <v>781</v>
       </c>
       <c r="D24" t="n">
-        <v>714</v>
+        <v>686</v>
       </c>
       <c r="E24" t="n">
-        <v>649</v>
+        <v>631</v>
       </c>
       <c r="F24" t="n">
-        <v>735</v>
+        <v>748</v>
       </c>
       <c r="G24" t="n">
-        <v>670</v>
+        <v>565</v>
       </c>
       <c r="H24" t="n">
-        <v>630</v>
+        <v>638</v>
       </c>
       <c r="I24" t="n">
-        <v>622</v>
+        <v>600</v>
       </c>
       <c r="J24" t="n">
-        <v>642</v>
+        <v>691</v>
       </c>
       <c r="K24" t="n">
-        <v>667</v>
+        <v>643</v>
       </c>
       <c r="L24" t="n">
-        <v>674.5</v>
+        <v>663.4</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>621</v>
+        <v>556</v>
       </c>
       <c r="C25" t="n">
-        <v>585</v>
+        <v>564</v>
       </c>
       <c r="D25" t="n">
-        <v>691</v>
+        <v>620</v>
       </c>
       <c r="E25" t="n">
-        <v>544</v>
+        <v>710</v>
       </c>
       <c r="F25" t="n">
-        <v>742</v>
+        <v>665</v>
       </c>
       <c r="G25" t="n">
-        <v>586</v>
+        <v>752</v>
       </c>
       <c r="H25" t="n">
-        <v>606</v>
+        <v>591</v>
       </c>
       <c r="I25" t="n">
-        <v>631</v>
+        <v>539</v>
       </c>
       <c r="J25" t="n">
-        <v>726</v>
+        <v>616</v>
       </c>
       <c r="K25" t="n">
-        <v>617</v>
+        <v>650</v>
       </c>
       <c r="L25" t="n">
-        <v>634.9</v>
+        <v>626.3</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>657</v>
+        <v>768</v>
       </c>
       <c r="C26" t="n">
-        <v>633</v>
+        <v>693</v>
       </c>
       <c r="D26" t="n">
-        <v>640</v>
+        <v>674</v>
       </c>
       <c r="E26" t="n">
-        <v>645</v>
+        <v>656</v>
       </c>
       <c r="F26" t="n">
-        <v>663</v>
+        <v>718</v>
       </c>
       <c r="G26" t="n">
-        <v>661</v>
+        <v>571</v>
       </c>
       <c r="H26" t="n">
-        <v>697</v>
+        <v>685</v>
       </c>
       <c r="I26" t="n">
-        <v>653</v>
+        <v>736</v>
       </c>
       <c r="J26" t="n">
-        <v>744</v>
+        <v>636</v>
       </c>
       <c r="K26" t="n">
-        <v>681</v>
+        <v>694</v>
       </c>
       <c r="L26" t="n">
-        <v>667.4</v>
+        <v>683.1</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>617</v>
+        <v>630</v>
       </c>
       <c r="C27" t="n">
-        <v>643</v>
+        <v>634</v>
       </c>
       <c r="D27" t="n">
+        <v>542</v>
+      </c>
+      <c r="E27" t="n">
+        <v>599</v>
+      </c>
+      <c r="F27" t="n">
         <v>649</v>
       </c>
-      <c r="E27" t="n">
-        <v>757</v>
-      </c>
-      <c r="F27" t="n">
-        <v>523</v>
-      </c>
       <c r="G27" t="n">
-        <v>619</v>
+        <v>585</v>
       </c>
       <c r="H27" t="n">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="I27" t="n">
-        <v>654</v>
+        <v>687</v>
       </c>
       <c r="J27" t="n">
-        <v>638</v>
+        <v>507</v>
       </c>
       <c r="K27" t="n">
-        <v>558</v>
+        <v>731</v>
       </c>
       <c r="L27" t="n">
-        <v>622.7</v>
+        <v>613.7</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>639</v>
+        <v>650</v>
       </c>
       <c r="C28" t="n">
-        <v>575</v>
+        <v>664</v>
       </c>
       <c r="D28" t="n">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="E28" t="n">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="F28" t="n">
-        <v>593</v>
+        <v>658</v>
       </c>
       <c r="G28" t="n">
-        <v>595</v>
+        <v>757</v>
       </c>
       <c r="H28" t="n">
-        <v>785</v>
+        <v>624</v>
       </c>
       <c r="I28" t="n">
-        <v>563</v>
+        <v>590</v>
       </c>
       <c r="J28" t="n">
-        <v>610</v>
+        <v>599</v>
       </c>
       <c r="K28" t="n">
-        <v>735</v>
+        <v>557</v>
       </c>
       <c r="L28" t="n">
-        <v>645.5</v>
+        <v>645.1</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>718</v>
+        <v>754</v>
       </c>
       <c r="C29" t="n">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="D29" t="n">
-        <v>653</v>
+        <v>731</v>
       </c>
       <c r="E29" t="n">
-        <v>703</v>
+        <v>674</v>
       </c>
       <c r="F29" t="n">
-        <v>742</v>
+        <v>723</v>
       </c>
       <c r="G29" t="n">
-        <v>613</v>
+        <v>729</v>
       </c>
       <c r="H29" t="n">
-        <v>612</v>
+        <v>692</v>
       </c>
       <c r="I29" t="n">
-        <v>707</v>
+        <v>631</v>
       </c>
       <c r="J29" t="n">
-        <v>704</v>
+        <v>733</v>
       </c>
       <c r="K29" t="n">
-        <v>747</v>
+        <v>656</v>
       </c>
       <c r="L29" t="n">
-        <v>689.4</v>
+        <v>701.9</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>593</v>
+        <v>664</v>
       </c>
       <c r="C30" t="n">
-        <v>671</v>
+        <v>776</v>
       </c>
       <c r="D30" t="n">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="E30" t="n">
-        <v>681</v>
+        <v>695</v>
       </c>
       <c r="F30" t="n">
-        <v>727</v>
+        <v>619</v>
       </c>
       <c r="G30" t="n">
-        <v>579</v>
+        <v>711</v>
       </c>
       <c r="H30" t="n">
-        <v>596</v>
+        <v>691</v>
       </c>
       <c r="I30" t="n">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="J30" t="n">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="K30" t="n">
-        <v>687</v>
+        <v>639</v>
       </c>
       <c r="L30" t="n">
-        <v>640.2</v>
+        <v>665.2</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>743</v>
+        <v>762</v>
       </c>
       <c r="C31" t="n">
-        <v>798</v>
+        <v>745</v>
       </c>
       <c r="D31" t="n">
-        <v>669</v>
+        <v>726</v>
       </c>
       <c r="E31" t="n">
-        <v>779</v>
+        <v>723</v>
       </c>
       <c r="F31" t="n">
-        <v>794</v>
+        <v>659</v>
       </c>
       <c r="G31" t="n">
-        <v>614</v>
+        <v>812</v>
       </c>
       <c r="H31" t="n">
-        <v>736</v>
+        <v>645</v>
       </c>
       <c r="I31" t="n">
-        <v>674</v>
+        <v>701</v>
       </c>
       <c r="J31" t="n">
         <v>704</v>
       </c>
       <c r="K31" t="n">
-        <v>724</v>
+        <v>685</v>
       </c>
       <c r="L31" t="n">
-        <v>723.5</v>
+        <v>716.2</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>729</v>
+        <v>630</v>
       </c>
       <c r="C32" t="n">
-        <v>720</v>
+        <v>708</v>
       </c>
       <c r="D32" t="n">
-        <v>705</v>
+        <v>683</v>
       </c>
       <c r="E32" t="n">
-        <v>637</v>
+        <v>651</v>
       </c>
       <c r="F32" t="n">
-        <v>730</v>
+        <v>693</v>
       </c>
       <c r="G32" t="n">
-        <v>745</v>
+        <v>671</v>
       </c>
       <c r="H32" t="n">
-        <v>692</v>
+        <v>715</v>
       </c>
       <c r="I32" t="n">
+        <v>678</v>
+      </c>
+      <c r="J32" t="n">
         <v>674</v>
       </c>
-      <c r="J32" t="n">
-        <v>599</v>
-      </c>
       <c r="K32" t="n">
-        <v>634</v>
+        <v>665</v>
       </c>
       <c r="L32" t="n">
-        <v>686.5</v>
+        <v>676.8</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>791</v>
+        <v>704</v>
       </c>
       <c r="C33" t="n">
-        <v>808</v>
+        <v>744</v>
       </c>
       <c r="D33" t="n">
-        <v>773</v>
+        <v>661</v>
       </c>
       <c r="E33" t="n">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="F33" t="n">
-        <v>669</v>
+        <v>831</v>
       </c>
       <c r="G33" t="n">
-        <v>692</v>
+        <v>685</v>
       </c>
       <c r="H33" t="n">
-        <v>661</v>
+        <v>728</v>
       </c>
       <c r="I33" t="n">
-        <v>692</v>
+        <v>719</v>
       </c>
       <c r="J33" t="n">
-        <v>758</v>
+        <v>694</v>
       </c>
       <c r="K33" t="n">
-        <v>759</v>
+        <v>682</v>
       </c>
       <c r="L33" t="n">
-        <v>728.1</v>
+        <v>713.2</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>732</v>
+        <v>613</v>
       </c>
       <c r="C34" t="n">
-        <v>507</v>
+        <v>640</v>
       </c>
       <c r="D34" t="n">
+        <v>802</v>
+      </c>
+      <c r="E34" t="n">
+        <v>656</v>
+      </c>
+      <c r="F34" t="n">
+        <v>760</v>
+      </c>
+      <c r="G34" t="n">
+        <v>656</v>
+      </c>
+      <c r="H34" t="n">
+        <v>627</v>
+      </c>
+      <c r="I34" t="n">
+        <v>836</v>
+      </c>
+      <c r="J34" t="n">
         <v>696</v>
       </c>
-      <c r="E34" t="n">
-        <v>740</v>
-      </c>
-      <c r="F34" t="n">
-        <v>846</v>
-      </c>
-      <c r="G34" t="n">
-        <v>736</v>
-      </c>
-      <c r="H34" t="n">
-        <v>615</v>
-      </c>
-      <c r="I34" t="n">
-        <v>691</v>
-      </c>
-      <c r="J34" t="n">
-        <v>653</v>
-      </c>
       <c r="K34" t="n">
-        <v>782</v>
+        <v>757</v>
       </c>
       <c r="L34" t="n">
-        <v>699.8</v>
+        <v>704.3</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>755</v>
+        <v>574</v>
       </c>
       <c r="C35" t="n">
-        <v>541</v>
+        <v>514</v>
       </c>
       <c r="D35" t="n">
-        <v>625</v>
+        <v>561</v>
       </c>
       <c r="E35" t="n">
-        <v>587</v>
+        <v>555</v>
       </c>
       <c r="F35" t="n">
-        <v>591</v>
+        <v>537</v>
       </c>
       <c r="G35" t="n">
-        <v>573</v>
+        <v>611</v>
       </c>
       <c r="H35" t="n">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="I35" t="n">
-        <v>538</v>
+        <v>584</v>
       </c>
       <c r="J35" t="n">
-        <v>534</v>
+        <v>584</v>
       </c>
       <c r="K35" t="n">
-        <v>676</v>
+        <v>594</v>
       </c>
       <c r="L35" t="n">
-        <v>595.3</v>
+        <v>564.3</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>774</v>
+        <v>725</v>
       </c>
       <c r="C36" t="n">
-        <v>751</v>
+        <v>614</v>
       </c>
       <c r="D36" t="n">
-        <v>764</v>
+        <v>729</v>
       </c>
       <c r="E36" t="n">
+        <v>718</v>
+      </c>
+      <c r="F36" t="n">
+        <v>632</v>
+      </c>
+      <c r="G36" t="n">
+        <v>679</v>
+      </c>
+      <c r="H36" t="n">
+        <v>635</v>
+      </c>
+      <c r="I36" t="n">
+        <v>706</v>
+      </c>
+      <c r="J36" t="n">
         <v>657</v>
       </c>
-      <c r="F36" t="n">
-        <v>732</v>
-      </c>
-      <c r="G36" t="n">
-        <v>617</v>
-      </c>
-      <c r="H36" t="n">
-        <v>809</v>
-      </c>
-      <c r="I36" t="n">
-        <v>719</v>
-      </c>
-      <c r="J36" t="n">
-        <v>756</v>
-      </c>
       <c r="K36" t="n">
-        <v>679</v>
+        <v>608</v>
       </c>
       <c r="L36" t="n">
-        <v>725.8</v>
+        <v>670.3</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>667</v>
+        <v>682</v>
       </c>
       <c r="C37" t="n">
-        <v>672</v>
+        <v>609</v>
       </c>
       <c r="D37" t="n">
-        <v>656</v>
+        <v>736</v>
       </c>
       <c r="E37" t="n">
-        <v>728</v>
+        <v>751</v>
       </c>
       <c r="F37" t="n">
-        <v>743</v>
+        <v>816</v>
       </c>
       <c r="G37" t="n">
-        <v>757</v>
+        <v>694</v>
       </c>
       <c r="H37" t="n">
-        <v>665</v>
+        <v>726</v>
       </c>
       <c r="I37" t="n">
-        <v>744</v>
+        <v>707</v>
       </c>
       <c r="J37" t="n">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="K37" t="n">
-        <v>733</v>
+        <v>648</v>
       </c>
       <c r="L37" t="n">
-        <v>704</v>
+        <v>704.5</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>679</v>
+        <v>654</v>
       </c>
       <c r="C38" t="n">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="D38" t="n">
-        <v>670</v>
+        <v>585</v>
       </c>
       <c r="E38" t="n">
-        <v>614</v>
+        <v>740</v>
       </c>
       <c r="F38" t="n">
-        <v>674</v>
+        <v>566</v>
       </c>
       <c r="G38" t="n">
-        <v>727</v>
+        <v>685</v>
       </c>
       <c r="H38" t="n">
-        <v>818</v>
+        <v>604</v>
       </c>
       <c r="I38" t="n">
-        <v>629</v>
+        <v>576</v>
       </c>
       <c r="J38" t="n">
-        <v>609</v>
+        <v>649</v>
       </c>
       <c r="K38" t="n">
-        <v>758</v>
+        <v>560</v>
       </c>
       <c r="L38" t="n">
-        <v>675.6</v>
+        <v>619.9</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>544</v>
+        <v>643</v>
       </c>
       <c r="C39" t="n">
-        <v>600</v>
+        <v>543</v>
       </c>
       <c r="D39" t="n">
-        <v>649</v>
+        <v>657</v>
       </c>
       <c r="E39" t="n">
-        <v>688</v>
+        <v>490</v>
       </c>
       <c r="F39" t="n">
-        <v>599</v>
+        <v>628</v>
       </c>
       <c r="G39" t="n">
-        <v>593</v>
+        <v>518</v>
       </c>
       <c r="H39" t="n">
-        <v>603</v>
+        <v>551</v>
       </c>
       <c r="I39" t="n">
-        <v>648</v>
+        <v>569</v>
       </c>
       <c r="J39" t="n">
-        <v>586</v>
+        <v>566</v>
       </c>
       <c r="K39" t="n">
-        <v>657</v>
+        <v>553</v>
       </c>
       <c r="L39" t="n">
-        <v>616.7</v>
+        <v>571.8</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>715</v>
+        <v>662</v>
       </c>
       <c r="C40" t="n">
-        <v>517</v>
+        <v>673</v>
       </c>
       <c r="D40" t="n">
-        <v>718</v>
+        <v>674</v>
       </c>
       <c r="E40" t="n">
-        <v>738</v>
+        <v>604</v>
       </c>
       <c r="F40" t="n">
-        <v>756</v>
+        <v>607</v>
       </c>
       <c r="G40" t="n">
-        <v>724</v>
+        <v>771</v>
       </c>
       <c r="H40" t="n">
+        <v>689</v>
+      </c>
+      <c r="I40" t="n">
+        <v>662</v>
+      </c>
+      <c r="J40" t="n">
         <v>571</v>
       </c>
-      <c r="I40" t="n">
-        <v>630</v>
-      </c>
-      <c r="J40" t="n">
-        <v>677</v>
-      </c>
       <c r="K40" t="n">
-        <v>678</v>
+        <v>662</v>
       </c>
       <c r="L40" t="n">
-        <v>672.4</v>
+        <v>657.5</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>818</v>
+        <v>692</v>
       </c>
       <c r="C41" t="n">
-        <v>589</v>
+        <v>641</v>
       </c>
       <c r="D41" t="n">
-        <v>732</v>
+        <v>605</v>
       </c>
       <c r="E41" t="n">
-        <v>671</v>
+        <v>577</v>
       </c>
       <c r="F41" t="n">
-        <v>622</v>
+        <v>683</v>
       </c>
       <c r="G41" t="n">
-        <v>678</v>
+        <v>598</v>
       </c>
       <c r="H41" t="n">
-        <v>572</v>
+        <v>693</v>
       </c>
       <c r="I41" t="n">
-        <v>716</v>
+        <v>634</v>
       </c>
       <c r="J41" t="n">
-        <v>660</v>
+        <v>586</v>
       </c>
       <c r="K41" t="n">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="L41" t="n">
-        <v>671.7</v>
+        <v>635.9</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>742</v>
+        <v>705</v>
       </c>
       <c r="C42" t="n">
-        <v>753</v>
+        <v>678</v>
       </c>
       <c r="D42" t="n">
-        <v>655</v>
+        <v>700</v>
       </c>
       <c r="E42" t="n">
-        <v>697</v>
+        <v>678</v>
       </c>
       <c r="F42" t="n">
-        <v>638</v>
+        <v>766</v>
       </c>
       <c r="G42" t="n">
-        <v>756</v>
+        <v>712</v>
       </c>
       <c r="H42" t="n">
-        <v>760</v>
+        <v>658</v>
       </c>
       <c r="I42" t="n">
-        <v>768</v>
+        <v>744</v>
       </c>
       <c r="J42" t="n">
-        <v>789</v>
+        <v>746</v>
       </c>
       <c r="K42" t="n">
-        <v>611</v>
+        <v>759</v>
       </c>
       <c r="L42" t="n">
-        <v>716.9</v>
+        <v>714.6</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>722</v>
+        <v>685</v>
       </c>
       <c r="C43" t="n">
-        <v>834</v>
+        <v>800</v>
       </c>
       <c r="D43" t="n">
-        <v>701</v>
+        <v>666</v>
       </c>
       <c r="E43" t="n">
-        <v>803</v>
+        <v>736</v>
       </c>
       <c r="F43" t="n">
-        <v>843</v>
+        <v>660</v>
       </c>
       <c r="G43" t="n">
-        <v>717</v>
+        <v>757</v>
       </c>
       <c r="H43" t="n">
+        <v>823</v>
+      </c>
+      <c r="I43" t="n">
         <v>745</v>
       </c>
-      <c r="I43" t="n">
-        <v>778</v>
-      </c>
       <c r="J43" t="n">
-        <v>741</v>
+        <v>604</v>
       </c>
       <c r="K43" t="n">
-        <v>763</v>
+        <v>756</v>
       </c>
       <c r="L43" t="n">
-        <v>764.7</v>
+        <v>723.2</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>643</v>
+        <v>753</v>
       </c>
       <c r="C44" t="n">
-        <v>649</v>
+        <v>605</v>
       </c>
       <c r="D44" t="n">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="E44" t="n">
-        <v>644</v>
+        <v>618</v>
       </c>
       <c r="F44" t="n">
-        <v>573</v>
+        <v>630</v>
       </c>
       <c r="G44" t="n">
-        <v>740</v>
+        <v>591</v>
       </c>
       <c r="H44" t="n">
-        <v>663</v>
+        <v>610</v>
       </c>
       <c r="I44" t="n">
-        <v>610</v>
+        <v>590</v>
       </c>
       <c r="J44" t="n">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="K44" t="n">
-        <v>700</v>
+        <v>658</v>
       </c>
       <c r="L44" t="n">
-        <v>651.2</v>
+        <v>635.2</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>667</v>
+        <v>705</v>
       </c>
       <c r="C45" t="n">
-        <v>690</v>
+        <v>722</v>
       </c>
       <c r="D45" t="n">
-        <v>801</v>
+        <v>742</v>
       </c>
       <c r="E45" t="n">
+        <v>668</v>
+      </c>
+      <c r="F45" t="n">
+        <v>713</v>
+      </c>
+      <c r="G45" t="n">
+        <v>727</v>
+      </c>
+      <c r="H45" t="n">
+        <v>623</v>
+      </c>
+      <c r="I45" t="n">
+        <v>735</v>
+      </c>
+      <c r="J45" t="n">
+        <v>638</v>
+      </c>
+      <c r="K45" t="n">
         <v>780</v>
       </c>
-      <c r="F45" t="n">
-        <v>757</v>
-      </c>
-      <c r="G45" t="n">
-        <v>673</v>
-      </c>
-      <c r="H45" t="n">
-        <v>714</v>
-      </c>
-      <c r="I45" t="n">
-        <v>775</v>
-      </c>
-      <c r="J45" t="n">
-        <v>699</v>
-      </c>
-      <c r="K45" t="n">
-        <v>690</v>
-      </c>
       <c r="L45" t="n">
-        <v>724.6</v>
+        <v>705.3</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>600</v>
+        <v>671</v>
       </c>
       <c r="C46" t="n">
-        <v>609</v>
+        <v>579</v>
       </c>
       <c r="D46" t="n">
-        <v>776</v>
+        <v>688</v>
       </c>
       <c r="E46" t="n">
-        <v>611</v>
+        <v>646</v>
       </c>
       <c r="F46" t="n">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="G46" t="n">
-        <v>658</v>
+        <v>563</v>
       </c>
       <c r="H46" t="n">
-        <v>699</v>
+        <v>567</v>
       </c>
       <c r="I46" t="n">
-        <v>643</v>
+        <v>692</v>
       </c>
       <c r="J46" t="n">
-        <v>644</v>
+        <v>657</v>
       </c>
       <c r="K46" t="n">
-        <v>619</v>
+        <v>573</v>
       </c>
       <c r="L46" t="n">
-        <v>654.2</v>
+        <v>632.3</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>630</v>
+        <v>619</v>
       </c>
       <c r="C47" t="n">
-        <v>651</v>
+        <v>637</v>
       </c>
       <c r="D47" t="n">
-        <v>649</v>
+        <v>631</v>
       </c>
       <c r="E47" t="n">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="F47" t="n">
-        <v>602</v>
+        <v>679</v>
       </c>
       <c r="G47" t="n">
+        <v>640</v>
+      </c>
+      <c r="H47" t="n">
+        <v>590</v>
+      </c>
+      <c r="I47" t="n">
+        <v>577</v>
+      </c>
+      <c r="J47" t="n">
         <v>682</v>
       </c>
-      <c r="H47" t="n">
-        <v>669</v>
-      </c>
-      <c r="I47" t="n">
-        <v>636</v>
-      </c>
-      <c r="J47" t="n">
-        <v>731</v>
-      </c>
       <c r="K47" t="n">
-        <v>702</v>
+        <v>579</v>
       </c>
       <c r="L47" t="n">
-        <v>650.2</v>
+        <v>619.1</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>730</v>
+        <v>768</v>
       </c>
       <c r="C48" t="n">
-        <v>812</v>
+        <v>825</v>
       </c>
       <c r="D48" t="n">
-        <v>771</v>
+        <v>852</v>
       </c>
       <c r="E48" t="n">
-        <v>724</v>
+        <v>814</v>
       </c>
       <c r="F48" t="n">
-        <v>792</v>
+        <v>822</v>
       </c>
       <c r="G48" t="n">
-        <v>816</v>
+        <v>676</v>
       </c>
       <c r="H48" t="n">
-        <v>802</v>
+        <v>791</v>
       </c>
       <c r="I48" t="n">
-        <v>737</v>
+        <v>803</v>
       </c>
       <c r="J48" t="n">
-        <v>727</v>
+        <v>791</v>
       </c>
       <c r="K48" t="n">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="L48" t="n">
-        <v>765.4</v>
+        <v>788.4</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>761</v>
+        <v>704</v>
       </c>
       <c r="C49" t="n">
+        <v>703</v>
+      </c>
+      <c r="D49" t="n">
+        <v>786</v>
+      </c>
+      <c r="E49" t="n">
+        <v>741</v>
+      </c>
+      <c r="F49" t="n">
+        <v>745</v>
+      </c>
+      <c r="G49" t="n">
+        <v>841</v>
+      </c>
+      <c r="H49" t="n">
+        <v>744</v>
+      </c>
+      <c r="I49" t="n">
         <v>721</v>
       </c>
-      <c r="D49" t="n">
-        <v>792</v>
-      </c>
-      <c r="E49" t="n">
-        <v>667</v>
-      </c>
-      <c r="F49" t="n">
-        <v>659</v>
-      </c>
-      <c r="G49" t="n">
-        <v>758</v>
-      </c>
-      <c r="H49" t="n">
-        <v>739</v>
-      </c>
-      <c r="I49" t="n">
-        <v>685</v>
-      </c>
       <c r="J49" t="n">
-        <v>738</v>
+        <v>749</v>
       </c>
       <c r="K49" t="n">
-        <v>688</v>
+        <v>800</v>
       </c>
       <c r="L49" t="n">
-        <v>720.8</v>
+        <v>753.4</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>688</v>
+        <v>662</v>
       </c>
       <c r="C50" t="n">
-        <v>805</v>
+        <v>711</v>
       </c>
       <c r="D50" t="n">
-        <v>723</v>
+        <v>683</v>
       </c>
       <c r="E50" t="n">
-        <v>686</v>
+        <v>771</v>
       </c>
       <c r="F50" t="n">
-        <v>737</v>
+        <v>649</v>
       </c>
       <c r="G50" t="n">
-        <v>605</v>
+        <v>693</v>
       </c>
       <c r="H50" t="n">
-        <v>564</v>
+        <v>705</v>
       </c>
       <c r="I50" t="n">
-        <v>720</v>
+        <v>655</v>
       </c>
       <c r="J50" t="n">
-        <v>642</v>
+        <v>588</v>
       </c>
       <c r="K50" t="n">
-        <v>726</v>
+        <v>659</v>
       </c>
       <c r="L50" t="n">
-        <v>689.6</v>
+        <v>677.6</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>750</v>
+        <v>690</v>
       </c>
       <c r="C51" t="n">
-        <v>686</v>
+        <v>709</v>
       </c>
       <c r="D51" t="n">
-        <v>690</v>
+        <v>747</v>
       </c>
       <c r="E51" t="n">
-        <v>633</v>
+        <v>617</v>
       </c>
       <c r="F51" t="n">
-        <v>658</v>
+        <v>691</v>
       </c>
       <c r="G51" t="n">
-        <v>645</v>
+        <v>628</v>
       </c>
       <c r="H51" t="n">
-        <v>688</v>
+        <v>629</v>
       </c>
       <c r="I51" t="n">
-        <v>691</v>
+        <v>555</v>
       </c>
       <c r="J51" t="n">
-        <v>720</v>
+        <v>641</v>
       </c>
       <c r="K51" t="n">
-        <v>689</v>
+        <v>639</v>
       </c>
       <c r="L51" t="n">
-        <v>685</v>
+        <v>654.6</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>677.02</v>
+        <v>671.64</v>
       </c>
       <c r="C52" t="n">
-        <v>669.92</v>
+        <v>659.26</v>
       </c>
       <c r="D52" t="n">
-        <v>671.64</v>
+        <v>676.86</v>
       </c>
       <c r="E52" t="n">
-        <v>666.34</v>
+        <v>652.16</v>
       </c>
       <c r="F52" t="n">
-        <v>686.42</v>
+        <v>670.58</v>
       </c>
       <c r="G52" t="n">
-        <v>669.76</v>
+        <v>666.92</v>
       </c>
       <c r="H52" t="n">
-        <v>665.84</v>
+        <v>650.2</v>
       </c>
       <c r="I52" t="n">
-        <v>664.66</v>
+        <v>654.1799999999999</v>
       </c>
       <c r="J52" t="n">
-        <v>676.7</v>
+        <v>655.9</v>
       </c>
       <c r="K52" t="n">
-        <v>678.78</v>
+        <v>657.74</v>
       </c>
       <c r="L52" t="n">
-        <v>672.7080000000001</v>
+        <v>661.544</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>4.592319250106812</v>
+        <v>4.558834552764893</v>
       </c>
       <c r="C2" t="n">
-        <v>4.24516749382019</v>
+        <v>4.459530830383301</v>
       </c>
       <c r="D2" t="n">
-        <v>4.821719408035278</v>
+        <v>4.715177297592163</v>
       </c>
       <c r="E2" t="n">
-        <v>4.323479890823364</v>
+        <v>4.506377220153809</v>
       </c>
       <c r="F2" t="n">
-        <v>4.317481279373169</v>
+        <v>4.8814377784729</v>
       </c>
       <c r="G2" t="n">
-        <v>4.893034934997559</v>
+        <v>4.565550327301025</v>
       </c>
       <c r="H2" t="n">
-        <v>4.377866983413696</v>
+        <v>4.75862193107605</v>
       </c>
       <c r="I2" t="n">
-        <v>4.698539018630981</v>
+        <v>4.416992664337158</v>
       </c>
       <c r="J2" t="n">
-        <v>4.360355854034424</v>
+        <v>4.316878318786621</v>
       </c>
       <c r="K2" t="n">
-        <v>4.176358699798584</v>
+        <v>5.400811195373535</v>
       </c>
       <c r="L2" t="n">
-        <v>4.480632281303405</v>
+        <v>4.658021211624146</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>4.406755208969116</v>
+        <v>4.39129638671875</v>
       </c>
       <c r="C3" t="n">
-        <v>4.67607593536377</v>
+        <v>5.154096841812134</v>
       </c>
       <c r="D3" t="n">
-        <v>4.659605741500854</v>
+        <v>4.803264856338501</v>
       </c>
       <c r="E3" t="n">
-        <v>4.502017021179199</v>
+        <v>4.45896315574646</v>
       </c>
       <c r="F3" t="n">
-        <v>4.992265701293945</v>
+        <v>4.748651266098022</v>
       </c>
       <c r="G3" t="n">
-        <v>4.555877923965454</v>
+        <v>4.689204931259155</v>
       </c>
       <c r="H3" t="n">
-        <v>5.571800708770752</v>
+        <v>5.139003753662109</v>
       </c>
       <c r="I3" t="n">
-        <v>4.595767021179199</v>
+        <v>4.698345184326172</v>
       </c>
       <c r="J3" t="n">
-        <v>4.615748882293701</v>
+        <v>4.809475421905518</v>
       </c>
       <c r="K3" t="n">
-        <v>4.748409032821655</v>
+        <v>4.605024576187134</v>
       </c>
       <c r="L3" t="n">
-        <v>4.732432317733765</v>
+        <v>4.749732637405396</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>3.916516542434692</v>
+        <v>3.813664436340332</v>
       </c>
       <c r="C4" t="n">
-        <v>3.743949413299561</v>
+        <v>3.98609733581543</v>
       </c>
       <c r="D4" t="n">
-        <v>4.498034000396729</v>
+        <v>4.969182014465332</v>
       </c>
       <c r="E4" t="n">
-        <v>3.989826440811157</v>
+        <v>4.39506983757019</v>
       </c>
       <c r="F4" t="n">
-        <v>4.200303077697754</v>
+        <v>3.869972467422485</v>
       </c>
       <c r="G4" t="n">
-        <v>4.449698686599731</v>
+        <v>3.864101409912109</v>
       </c>
       <c r="H4" t="n">
-        <v>3.592895030975342</v>
+        <v>4.475997447967529</v>
       </c>
       <c r="I4" t="n">
-        <v>4.362375974655151</v>
+        <v>4.093853950500488</v>
       </c>
       <c r="J4" t="n">
-        <v>4.34791374206543</v>
+        <v>3.709993362426758</v>
       </c>
       <c r="K4" t="n">
-        <v>4.740398168563843</v>
+        <v>4.743980169296265</v>
       </c>
       <c r="L4" t="n">
-        <v>4.184191107749939</v>
+        <v>4.192191243171692</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>3.926000833511353</v>
+        <v>4.452043533325195</v>
       </c>
       <c r="C5" t="n">
-        <v>4.367704391479492</v>
+        <v>4.340534448623657</v>
       </c>
       <c r="D5" t="n">
-        <v>4.50480580329895</v>
+        <v>4.598707675933838</v>
       </c>
       <c r="E5" t="n">
-        <v>4.407535076141357</v>
+        <v>4.279811143875122</v>
       </c>
       <c r="F5" t="n">
-        <v>3.996588468551636</v>
+        <v>4.589935541152954</v>
       </c>
       <c r="G5" t="n">
-        <v>4.347178220748901</v>
+        <v>4.023788452148438</v>
       </c>
       <c r="H5" t="n">
-        <v>4.190115690231323</v>
+        <v>4.519980192184448</v>
       </c>
       <c r="I5" t="n">
-        <v>4.61995792388916</v>
+        <v>4.550664186477661</v>
       </c>
       <c r="J5" t="n">
-        <v>4.070898056030273</v>
+        <v>4.240254402160645</v>
       </c>
       <c r="K5" t="n">
-        <v>4.388572216033936</v>
+        <v>4.289474487304688</v>
       </c>
       <c r="L5" t="n">
-        <v>4.281935667991638</v>
+        <v>4.388519406318665</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>3.817461013793945</v>
+        <v>5.824338674545288</v>
       </c>
       <c r="C6" t="n">
-        <v>3.9414381980896</v>
+        <v>4.020519495010376</v>
       </c>
       <c r="D6" t="n">
-        <v>4.266643285751343</v>
+        <v>4.05246376991272</v>
       </c>
       <c r="E6" t="n">
-        <v>4.274080991744995</v>
+        <v>4.041991949081421</v>
       </c>
       <c r="F6" t="n">
-        <v>4.185330867767334</v>
+        <v>4.256917238235474</v>
       </c>
       <c r="G6" t="n">
-        <v>4.577321290969849</v>
+        <v>4.121786832809448</v>
       </c>
       <c r="H6" t="n">
-        <v>4.61223030090332</v>
+        <v>4.64293384552002</v>
       </c>
       <c r="I6" t="n">
-        <v>4.393301963806152</v>
+        <v>8.901641607284546</v>
       </c>
       <c r="J6" t="n">
-        <v>4.093050718307495</v>
+        <v>4.105818271636963</v>
       </c>
       <c r="K6" t="n">
-        <v>4.227215766906738</v>
+        <v>4.29235053062439</v>
       </c>
       <c r="L6" t="n">
-        <v>4.238807439804077</v>
+        <v>4.826076221466065</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>4.087069749832153</v>
+        <v>4.704242706298828</v>
       </c>
       <c r="C7" t="n">
-        <v>4.544410943984985</v>
+        <v>3.839995622634888</v>
       </c>
       <c r="D7" t="n">
-        <v>4.091558694839478</v>
+        <v>4.13226318359375</v>
       </c>
       <c r="E7" t="n">
-        <v>3.868631362915039</v>
+        <v>4.279850482940674</v>
       </c>
       <c r="F7" t="n">
-        <v>4.00981068611145</v>
+        <v>4.057958126068115</v>
       </c>
       <c r="G7" t="n">
-        <v>4.88702654838562</v>
+        <v>4.772563934326172</v>
       </c>
       <c r="H7" t="n">
-        <v>4.037686347961426</v>
+        <v>3.913356304168701</v>
       </c>
       <c r="I7" t="n">
-        <v>3.959401607513428</v>
+        <v>3.891870737075806</v>
       </c>
       <c r="J7" t="n">
-        <v>3.773390054702759</v>
+        <v>3.926776885986328</v>
       </c>
       <c r="K7" t="n">
-        <v>4.230231046676636</v>
+        <v>3.852970838546753</v>
       </c>
       <c r="L7" t="n">
-        <v>4.148921704292297</v>
+        <v>4.137184882164002</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>4.161880493164062</v>
+        <v>5.32664155960083</v>
       </c>
       <c r="C8" t="n">
-        <v>4.440673112869263</v>
+        <v>5.182498216629028</v>
       </c>
       <c r="D8" t="n">
-        <v>4.033236503601074</v>
+        <v>4.235970497131348</v>
       </c>
       <c r="E8" t="n">
-        <v>4.163509607315063</v>
+        <v>4.340724468231201</v>
       </c>
       <c r="F8" t="n">
-        <v>4.406755685806274</v>
+        <v>3.986120462417603</v>
       </c>
       <c r="G8" t="n">
-        <v>4.405767917633057</v>
+        <v>4.125259160995483</v>
       </c>
       <c r="H8" t="n">
-        <v>5.065584659576416</v>
+        <v>4.172632217407227</v>
       </c>
       <c r="I8" t="n">
-        <v>4.215243577957153</v>
+        <v>4.523719549179077</v>
       </c>
       <c r="J8" t="n">
-        <v>4.268098592758179</v>
+        <v>4.274376392364502</v>
       </c>
       <c r="K8" t="n">
-        <v>4.383914232254028</v>
+        <v>4.275377988815308</v>
       </c>
       <c r="L8" t="n">
-        <v>4.354466438293457</v>
+        <v>4.44433205127716</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>3.64462423324585</v>
+        <v>3.733765125274658</v>
       </c>
       <c r="C9" t="n">
-        <v>3.740749597549438</v>
+        <v>3.955838203430176</v>
       </c>
       <c r="D9" t="n">
-        <v>4.006998538970947</v>
+        <v>3.814119815826416</v>
       </c>
       <c r="E9" t="n">
-        <v>4.203268527984619</v>
+        <v>3.929767608642578</v>
       </c>
       <c r="F9" t="n">
-        <v>3.918493986129761</v>
+        <v>4.073408842086792</v>
       </c>
       <c r="G9" t="n">
-        <v>4.095084190368652</v>
+        <v>3.612593173980713</v>
       </c>
       <c r="H9" t="n">
-        <v>3.898570775985718</v>
+        <v>3.722319841384888</v>
       </c>
       <c r="I9" t="n">
-        <v>3.963387727737427</v>
+        <v>3.917303562164307</v>
       </c>
       <c r="J9" t="n">
-        <v>3.676119327545166</v>
+        <v>4.264894723892212</v>
       </c>
       <c r="K9" t="n">
-        <v>3.640707015991211</v>
+        <v>4.045961141586304</v>
       </c>
       <c r="L9" t="n">
-        <v>3.878800392150879</v>
+        <v>3.906997203826904</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>4.747907638549805</v>
+        <v>5.244371175765991</v>
       </c>
       <c r="C10" t="n">
-        <v>5.143360614776611</v>
+        <v>4.937635183334351</v>
       </c>
       <c r="D10" t="n">
-        <v>5.410235643386841</v>
+        <v>5.307676792144775</v>
       </c>
       <c r="E10" t="n">
-        <v>5.600724220275879</v>
+        <v>5.171560049057007</v>
       </c>
       <c r="F10" t="n">
-        <v>5.469039440155029</v>
+        <v>5.047852993011475</v>
       </c>
       <c r="G10" t="n">
-        <v>4.915960311889648</v>
+        <v>5.153569221496582</v>
       </c>
       <c r="H10" t="n">
-        <v>4.799747943878174</v>
+        <v>4.90074610710144</v>
       </c>
       <c r="I10" t="n">
-        <v>5.038691282272339</v>
+        <v>5.147088050842285</v>
       </c>
       <c r="J10" t="n">
-        <v>4.876552104949951</v>
+        <v>4.926676273345947</v>
       </c>
       <c r="K10" t="n">
-        <v>5.455598831176758</v>
+        <v>5.168542623519897</v>
       </c>
       <c r="L10" t="n">
-        <v>5.145781803131103</v>
+        <v>5.100571846961975</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>4.462598562240601</v>
+        <v>5.215460300445557</v>
       </c>
       <c r="C11" t="n">
-        <v>4.343919277191162</v>
+        <v>4.539673328399658</v>
       </c>
       <c r="D11" t="n">
-        <v>4.980797290802002</v>
+        <v>5.463269948959351</v>
       </c>
       <c r="E11" t="n">
-        <v>5.304953575134277</v>
+        <v>5.121170520782471</v>
       </c>
       <c r="F11" t="n">
-        <v>4.751888036727905</v>
+        <v>4.936647415161133</v>
       </c>
       <c r="G11" t="n">
-        <v>5.199735879898071</v>
+        <v>4.265723943710327</v>
       </c>
       <c r="H11" t="n">
-        <v>4.766340732574463</v>
+        <v>4.928921222686768</v>
       </c>
       <c r="I11" t="n">
-        <v>4.351902723312378</v>
+        <v>4.405759572982788</v>
       </c>
       <c r="J11" t="n">
-        <v>4.884532451629639</v>
+        <v>4.80274772644043</v>
       </c>
       <c r="K11" t="n">
-        <v>4.593320608139038</v>
+        <v>4.267616033554077</v>
       </c>
       <c r="L11" t="n">
-        <v>4.763998913764953</v>
+        <v>4.794699001312256</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>4.228735685348511</v>
+        <v>4.37732982635498</v>
       </c>
       <c r="C12" t="n">
-        <v>4.422742366790771</v>
+        <v>4.108031511306763</v>
       </c>
       <c r="D12" t="n">
-        <v>4.830674886703491</v>
+        <v>4.024740219116211</v>
       </c>
       <c r="E12" t="n">
-        <v>4.220237970352173</v>
+        <v>3.937485694885254</v>
       </c>
       <c r="F12" t="n">
-        <v>4.258639812469482</v>
+        <v>3.984851598739624</v>
       </c>
       <c r="G12" t="n">
-        <v>4.139932870864868</v>
+        <v>4.14193320274353</v>
       </c>
       <c r="H12" t="n">
-        <v>4.192302227020264</v>
+        <v>4.138266801834106</v>
       </c>
       <c r="I12" t="n">
-        <v>4.423730850219727</v>
+        <v>4.455890417098999</v>
       </c>
       <c r="J12" t="n">
-        <v>4.80375075340271</v>
+        <v>3.996095895767212</v>
       </c>
       <c r="K12" t="n">
-        <v>3.996816158294678</v>
+        <v>4.285849094390869</v>
       </c>
       <c r="L12" t="n">
-        <v>4.351756358146668</v>
+        <v>4.145047426223755</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>5.686478614807129</v>
+        <v>5.168539047241211</v>
       </c>
       <c r="C13" t="n">
-        <v>5.345372915267944</v>
+        <v>4.924665212631226</v>
       </c>
       <c r="D13" t="n">
-        <v>5.229679107666016</v>
+        <v>4.772566080093384</v>
       </c>
       <c r="E13" t="n">
-        <v>4.729455471038818</v>
+        <v>5.248396396636963</v>
       </c>
       <c r="F13" t="n">
-        <v>5.383301019668579</v>
+        <v>5.108217239379883</v>
       </c>
       <c r="G13" t="n">
-        <v>4.993252277374268</v>
+        <v>5.723618984222412</v>
       </c>
       <c r="H13" t="n">
-        <v>4.874567031860352</v>
+        <v>5.404946565628052</v>
       </c>
       <c r="I13" t="n">
-        <v>5.410196781158447</v>
+        <v>5.236361742019653</v>
       </c>
       <c r="J13" t="n">
-        <v>5.560820817947388</v>
+        <v>4.932178258895874</v>
       </c>
       <c r="K13" t="n">
-        <v>5.440131187438965</v>
+        <v>5.082772016525269</v>
       </c>
       <c r="L13" t="n">
-        <v>5.26532552242279</v>
+        <v>5.160226154327392</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>4.4246985912323</v>
+        <v>4.898465156555176</v>
       </c>
       <c r="C14" t="n">
-        <v>5.426174879074097</v>
+        <v>4.151419162750244</v>
       </c>
       <c r="D14" t="n">
-        <v>4.445155620574951</v>
+        <v>5.362887382507324</v>
       </c>
       <c r="E14" t="n">
-        <v>4.567826747894287</v>
+        <v>4.373847484588623</v>
       </c>
       <c r="F14" t="n">
-        <v>4.461127758026123</v>
+        <v>4.855639696121216</v>
       </c>
       <c r="G14" t="n">
-        <v>4.736421585083008</v>
+        <v>4.612277507781982</v>
       </c>
       <c r="H14" t="n">
-        <v>5.293020248413086</v>
+        <v>4.29058313369751</v>
       </c>
       <c r="I14" t="n">
-        <v>5.366796731948853</v>
+        <v>4.398773193359375</v>
       </c>
       <c r="J14" t="n">
-        <v>4.298532724380493</v>
+        <v>4.917971134185791</v>
       </c>
       <c r="K14" t="n">
-        <v>5.020195960998535</v>
+        <v>5.291030883789062</v>
       </c>
       <c r="L14" t="n">
-        <v>4.803995084762573</v>
+        <v>4.71528947353363</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>4.62719464302063</v>
+        <v>5.033171415328979</v>
       </c>
       <c r="C15" t="n">
-        <v>4.687539339065552</v>
+        <v>5.135419845581055</v>
       </c>
       <c r="D15" t="n">
-        <v>5.137385129928589</v>
+        <v>4.868099927902222</v>
       </c>
       <c r="E15" t="n">
-        <v>5.192781925201416</v>
+        <v>4.848658084869385</v>
       </c>
       <c r="F15" t="n">
-        <v>4.703529357910156</v>
+        <v>4.655647039413452</v>
       </c>
       <c r="G15" t="n">
-        <v>4.950367450714111</v>
+        <v>4.581826210021973</v>
       </c>
       <c r="H15" t="n">
-        <v>5.007236480712891</v>
+        <v>5.383260250091553</v>
       </c>
       <c r="I15" t="n">
-        <v>4.82469367980957</v>
+        <v>4.765873908996582</v>
       </c>
       <c r="J15" t="n">
-        <v>5.298498153686523</v>
+        <v>5.167323350906372</v>
       </c>
       <c r="K15" t="n">
-        <v>4.853119373321533</v>
+        <v>4.585313320159912</v>
       </c>
       <c r="L15" t="n">
-        <v>4.928234553337097</v>
+        <v>4.902459335327149</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>4.471111297607422</v>
+        <v>4.699536085128784</v>
       </c>
       <c r="C16" t="n">
-        <v>4.260151386260986</v>
+        <v>4.411506175994873</v>
       </c>
       <c r="D16" t="n">
-        <v>4.214243173599243</v>
+        <v>4.154401302337646</v>
       </c>
       <c r="E16" t="n">
-        <v>3.998839855194092</v>
+        <v>4.832670450210571</v>
       </c>
       <c r="F16" t="n">
-        <v>5.21570611000061</v>
+        <v>4.299537181854248</v>
       </c>
       <c r="G16" t="n">
-        <v>4.508002758026123</v>
+        <v>5.329896211624146</v>
       </c>
       <c r="H16" t="n">
-        <v>4.366897106170654</v>
+        <v>4.223363637924194</v>
       </c>
       <c r="I16" t="n">
-        <v>4.931911468505859</v>
+        <v>4.135947704315186</v>
       </c>
       <c r="J16" t="n">
-        <v>4.472626209259033</v>
+        <v>4.422726631164551</v>
       </c>
       <c r="K16" t="n">
-        <v>4.738913536071777</v>
+        <v>4.049178600311279</v>
       </c>
       <c r="L16" t="n">
-        <v>4.51784029006958</v>
+        <v>4.455876398086548</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>4.767347812652588</v>
+        <v>4.455140352249146</v>
       </c>
       <c r="C17" t="n">
-        <v>4.815239667892456</v>
+        <v>4.343411922454834</v>
       </c>
       <c r="D17" t="n">
-        <v>4.328500747680664</v>
+        <v>4.797751426696777</v>
       </c>
       <c r="E17" t="n">
-        <v>5.22966742515564</v>
+        <v>4.208288908004761</v>
       </c>
       <c r="F17" t="n">
-        <v>5.002222061157227</v>
+        <v>5.75881028175354</v>
       </c>
       <c r="G17" t="n">
-        <v>4.369354724884033</v>
+        <v>4.454144716262817</v>
       </c>
       <c r="H17" t="n">
-        <v>4.224207639694214</v>
+        <v>4.248151779174805</v>
       </c>
       <c r="I17" t="n">
-        <v>4.555383920669556</v>
+        <v>4.413758993148804</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735414028167725</v>
+        <v>4.404772758483887</v>
       </c>
       <c r="K17" t="n">
-        <v>4.352902173995972</v>
+        <v>4.393809795379639</v>
       </c>
       <c r="L17" t="n">
-        <v>4.638024020195007</v>
+        <v>4.547804093360901</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>4.835661888122559</v>
+        <v>5.000253200531006</v>
       </c>
       <c r="C18" t="n">
-        <v>4.723438739776611</v>
+        <v>4.288583993911743</v>
       </c>
       <c r="D18" t="n">
-        <v>4.585301399230957</v>
+        <v>4.399816989898682</v>
       </c>
       <c r="E18" t="n">
-        <v>4.968825578689575</v>
+        <v>4.432689428329468</v>
       </c>
       <c r="F18" t="n">
-        <v>4.998355150222778</v>
+        <v>5.128455877304077</v>
       </c>
       <c r="G18" t="n">
-        <v>4.750899791717529</v>
+        <v>4.920958995819092</v>
       </c>
       <c r="H18" t="n">
-        <v>4.662144899368286</v>
+        <v>4.599292278289795</v>
       </c>
       <c r="I18" t="n">
-        <v>4.30352520942688</v>
+        <v>4.898035526275635</v>
       </c>
       <c r="J18" t="n">
-        <v>4.999260425567627</v>
+        <v>4.623221874237061</v>
       </c>
       <c r="K18" t="n">
-        <v>4.630197286605835</v>
+        <v>4.77582049369812</v>
       </c>
       <c r="L18" t="n">
-        <v>4.745761036872864</v>
+        <v>4.706712865829468</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>5.095518350601196</v>
+        <v>4.407754898071289</v>
       </c>
       <c r="C19" t="n">
-        <v>4.721467971801758</v>
+        <v>4.52597713470459</v>
       </c>
       <c r="D19" t="n">
-        <v>4.149419784545898</v>
+        <v>4.617220163345337</v>
       </c>
       <c r="E19" t="n">
-        <v>4.48455548286438</v>
+        <v>4.273604154586792</v>
       </c>
       <c r="F19" t="n">
-        <v>4.804728746414185</v>
+        <v>4.655115604400635</v>
       </c>
       <c r="G19" t="n">
-        <v>4.4740891456604</v>
+        <v>4.561375617980957</v>
       </c>
       <c r="H19" t="n">
-        <v>4.377819061279297</v>
+        <v>4.108046770095825</v>
       </c>
       <c r="I19" t="n">
-        <v>4.804779052734375</v>
+        <v>4.204279661178589</v>
       </c>
       <c r="J19" t="n">
-        <v>4.998725652694702</v>
+        <v>4.218242883682251</v>
       </c>
       <c r="K19" t="n">
-        <v>5.125943660736084</v>
+        <v>4.369344711303711</v>
       </c>
       <c r="L19" t="n">
-        <v>4.703704690933227</v>
+        <v>4.394096159934998</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>4.895044088363647</v>
+        <v>5.239212512969971</v>
       </c>
       <c r="C20" t="n">
-        <v>5.269095659255981</v>
+        <v>5.62668514251709</v>
       </c>
       <c r="D20" t="n">
-        <v>5.082309007644653</v>
+        <v>5.08055567741394</v>
       </c>
       <c r="E20" t="n">
-        <v>4.680353403091431</v>
+        <v>4.958849430084229</v>
       </c>
       <c r="F20" t="n">
-        <v>5.595589637756348</v>
+        <v>5.338873147964478</v>
       </c>
       <c r="G20" t="n">
-        <v>5.037400960922241</v>
+        <v>5.502528190612793</v>
       </c>
       <c r="H20" t="n">
-        <v>5.010957956314087</v>
+        <v>4.926932811737061</v>
       </c>
       <c r="I20" t="n">
-        <v>5.116183042526245</v>
+        <v>5.710938453674316</v>
       </c>
       <c r="J20" t="n">
-        <v>4.849364280700684</v>
+        <v>4.759867668151855</v>
       </c>
       <c r="K20" t="n">
-        <v>5.3326416015625</v>
+        <v>5.455077648162842</v>
       </c>
       <c r="L20" t="n">
-        <v>5.086893963813782</v>
+        <v>5.259952068328857</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>4.531009197235107</v>
+        <v>4.518001556396484</v>
       </c>
       <c r="C21" t="n">
-        <v>5.009225845336914</v>
+        <v>5.245627641677856</v>
       </c>
       <c r="D21" t="n">
-        <v>4.393810033798218</v>
+        <v>4.952895164489746</v>
       </c>
       <c r="E21" t="n">
-        <v>4.585310935974121</v>
+        <v>4.379819393157959</v>
       </c>
       <c r="F21" t="n">
-        <v>4.51197624206543</v>
+        <v>4.211296319961548</v>
       </c>
       <c r="G21" t="n">
-        <v>4.563348293304443</v>
+        <v>4.52495288848877</v>
       </c>
       <c r="H21" t="n">
-        <v>4.129968643188477</v>
+        <v>4.732440710067749</v>
       </c>
       <c r="I21" t="n">
-        <v>4.109030961990356</v>
+        <v>4.768848896026611</v>
       </c>
       <c r="J21" t="n">
-        <v>4.643148422241211</v>
+        <v>5.009237289428711</v>
       </c>
       <c r="K21" t="n">
-        <v>4.710468053817749</v>
+        <v>4.29255199432373</v>
       </c>
       <c r="L21" t="n">
-        <v>4.518729662895202</v>
+        <v>4.663567185401917</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>4.482055902481079</v>
+        <v>5.136438369750977</v>
       </c>
       <c r="C22" t="n">
-        <v>4.880073547363281</v>
+        <v>4.671602010726929</v>
       </c>
       <c r="D22" t="n">
-        <v>4.831696271896362</v>
+        <v>4.513989210128784</v>
       </c>
       <c r="E22" t="n">
-        <v>5.300976037979126</v>
+        <v>4.950871467590332</v>
       </c>
       <c r="F22" t="n">
-        <v>5.629633188247681</v>
+        <v>4.653658866882324</v>
       </c>
       <c r="G22" t="n">
-        <v>4.958842039108276</v>
+        <v>4.990278482437134</v>
       </c>
       <c r="H22" t="n">
-        <v>4.509997129440308</v>
+        <v>4.513975381851196</v>
       </c>
       <c r="I22" t="n">
-        <v>4.177350997924805</v>
+        <v>5.124436378479004</v>
       </c>
       <c r="J22" t="n">
-        <v>4.655143737792969</v>
+        <v>4.971811532974243</v>
       </c>
       <c r="K22" t="n">
-        <v>4.981292247772217</v>
+        <v>4.415737152099609</v>
       </c>
       <c r="L22" t="n">
-        <v>4.84070611000061</v>
+        <v>4.794279885292053</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>3.979847431182861</v>
+        <v>4.260121822357178</v>
       </c>
       <c r="C23" t="n">
-        <v>4.351398468017578</v>
+        <v>4.447664737701416</v>
       </c>
       <c r="D23" t="n">
-        <v>4.140460968017578</v>
+        <v>4.096053838729858</v>
       </c>
       <c r="E23" t="n">
-        <v>4.755366086959839</v>
+        <v>4.352905035018921</v>
       </c>
       <c r="F23" t="n">
-        <v>4.575358390808105</v>
+        <v>4.361998319625854</v>
       </c>
       <c r="G23" t="n">
-        <v>4.503037691116333</v>
+        <v>4.35089898109436</v>
       </c>
       <c r="H23" t="n">
-        <v>4.781301498413086</v>
+        <v>4.076627254486084</v>
       </c>
       <c r="I23" t="n">
-        <v>4.062174320220947</v>
+        <v>4.39879846572876</v>
       </c>
       <c r="J23" t="n">
-        <v>4.179842472076416</v>
+        <v>4.81873345375061</v>
       </c>
       <c r="K23" t="n">
-        <v>4.352916717529297</v>
+        <v>4.846171140670776</v>
       </c>
       <c r="L23" t="n">
-        <v>4.368170404434204</v>
+        <v>4.400997304916382</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>4.989275217056274</v>
+        <v>4.618253469467163</v>
       </c>
       <c r="C24" t="n">
-        <v>4.69853687286377</v>
+        <v>5.009235143661499</v>
       </c>
       <c r="D24" t="n">
-        <v>4.617207288742065</v>
+        <v>4.688542127609253</v>
       </c>
       <c r="E24" t="n">
-        <v>4.410771131515503</v>
+        <v>4.660131931304932</v>
       </c>
       <c r="F24" t="n">
-        <v>4.51198410987854</v>
+        <v>4.805733442306519</v>
       </c>
       <c r="G24" t="n">
-        <v>4.814713954925537</v>
+        <v>4.417740821838379</v>
       </c>
       <c r="H24" t="n">
-        <v>4.625186920166016</v>
+        <v>4.584307432174683</v>
       </c>
       <c r="I24" t="n">
-        <v>5.171850204467773</v>
+        <v>4.905004978179932</v>
       </c>
       <c r="J24" t="n">
-        <v>4.966839790344238</v>
+        <v>4.731469392776489</v>
       </c>
       <c r="K24" t="n">
-        <v>4.784799575805664</v>
+        <v>4.465179920196533</v>
       </c>
       <c r="L24" t="n">
-        <v>4.759116506576538</v>
+        <v>4.688559865951538</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>4.465150833129883</v>
+        <v>4.645191192626953</v>
       </c>
       <c r="C25" t="n">
-        <v>4.469362497329712</v>
+        <v>4.197304964065552</v>
       </c>
       <c r="D25" t="n">
-        <v>4.685300827026367</v>
+        <v>4.638170480728149</v>
       </c>
       <c r="E25" t="n">
-        <v>4.224001884460449</v>
+        <v>5.554868936538696</v>
       </c>
       <c r="F25" t="n">
-        <v>4.856352567672729</v>
+        <v>4.575863122940063</v>
       </c>
       <c r="G25" t="n">
-        <v>4.408517122268677</v>
+        <v>4.931448459625244</v>
       </c>
       <c r="H25" t="n">
-        <v>4.35366153717041</v>
+        <v>4.349411964416504</v>
       </c>
       <c r="I25" t="n">
-        <v>4.368119955062866</v>
+        <v>4.352895021438599</v>
       </c>
       <c r="J25" t="n">
-        <v>5.156265258789062</v>
+        <v>4.383314371109009</v>
       </c>
       <c r="K25" t="n">
-        <v>4.290562868118286</v>
+        <v>5.172803163528442</v>
       </c>
       <c r="L25" t="n">
-        <v>4.527729535102845</v>
+        <v>4.680127167701722</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>4.633705377578735</v>
+        <v>5.121472120285034</v>
       </c>
       <c r="C26" t="n">
-        <v>4.425702095031738</v>
+        <v>4.686542749404907</v>
       </c>
       <c r="D26" t="n">
-        <v>4.461618423461914</v>
+        <v>4.597291946411133</v>
       </c>
       <c r="E26" t="n">
-        <v>4.648652315139771</v>
+        <v>4.548954248428345</v>
       </c>
       <c r="F26" t="n">
-        <v>4.879573106765747</v>
+        <v>4.522965431213379</v>
       </c>
       <c r="G26" t="n">
-        <v>5.197764873504639</v>
+        <v>4.256645917892456</v>
       </c>
       <c r="H26" t="n">
-        <v>4.635174751281738</v>
+        <v>4.534926891326904</v>
       </c>
       <c r="I26" t="n">
-        <v>4.574336767196655</v>
+        <v>4.63918137550354</v>
       </c>
       <c r="J26" t="n">
-        <v>5.472541570663452</v>
+        <v>4.82720947265625</v>
       </c>
       <c r="K26" t="n">
-        <v>5.050115346908569</v>
+        <v>5.240629911422729</v>
       </c>
       <c r="L26" t="n">
-        <v>4.797918462753296</v>
+        <v>4.697582006454468</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>4.529933214187622</v>
+        <v>4.522998809814453</v>
       </c>
       <c r="C27" t="n">
-        <v>4.444188356399536</v>
+        <v>4.295560598373413</v>
       </c>
       <c r="D27" t="n">
-        <v>4.733418464660645</v>
+        <v>4.145434141159058</v>
       </c>
       <c r="E27" t="n">
-        <v>4.83469295501709</v>
+        <v>4.147936820983887</v>
       </c>
       <c r="F27" t="n">
-        <v>3.920494556427002</v>
+        <v>4.70451283454895</v>
       </c>
       <c r="G27" t="n">
-        <v>4.653720855712891</v>
+        <v>4.052648305892944</v>
       </c>
       <c r="H27" t="n">
-        <v>4.484071731567383</v>
+        <v>3.98386549949646</v>
       </c>
       <c r="I27" t="n">
-        <v>5.025172233581543</v>
+        <v>4.770856380462646</v>
       </c>
       <c r="J27" t="n">
-        <v>4.503014802932739</v>
+        <v>3.949425458908081</v>
       </c>
       <c r="K27" t="n">
-        <v>4.215242385864258</v>
+        <v>4.595304489135742</v>
       </c>
       <c r="L27" t="n">
-        <v>4.53439495563507</v>
+        <v>4.316854333877563</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>4.269092559814453</v>
+        <v>4.325464725494385</v>
       </c>
       <c r="C28" t="n">
-        <v>4.426693916320801</v>
+        <v>4.282611608505249</v>
       </c>
       <c r="D28" t="n">
-        <v>4.46710991859436</v>
+        <v>4.592308044433594</v>
       </c>
       <c r="E28" t="n">
-        <v>4.512004375457764</v>
+        <v>4.825696706771851</v>
       </c>
       <c r="F28" t="n">
-        <v>4.125991582870483</v>
+        <v>4.410744905471802</v>
       </c>
       <c r="G28" t="n">
-        <v>4.147442579269409</v>
+        <v>6.163877964019775</v>
       </c>
       <c r="H28" t="n">
-        <v>5.313944101333618</v>
+        <v>4.538198232650757</v>
       </c>
       <c r="I28" t="n">
-        <v>4.214270830154419</v>
+        <v>4.249917268753052</v>
       </c>
       <c r="J28" t="n">
-        <v>4.112000226974487</v>
+        <v>4.051475763320923</v>
       </c>
       <c r="K28" t="n">
-        <v>4.433671951293945</v>
+        <v>4.244472742080688</v>
       </c>
       <c r="L28" t="n">
-        <v>4.402222204208374</v>
+        <v>4.568476796150208</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>5.708964109420776</v>
+        <v>4.592101335525513</v>
       </c>
       <c r="C29" t="n">
-        <v>4.846658229827881</v>
+        <v>4.575875759124756</v>
       </c>
       <c r="D29" t="n">
-        <v>4.178337812423706</v>
+        <v>4.611982107162476</v>
       </c>
       <c r="E29" t="n">
-        <v>4.242190837860107</v>
+        <v>4.488818407058716</v>
       </c>
       <c r="F29" t="n">
-        <v>4.68954610824585</v>
+        <v>4.445934295654297</v>
       </c>
       <c r="G29" t="n">
-        <v>4.330446004867554</v>
+        <v>4.800989866256714</v>
       </c>
       <c r="H29" t="n">
-        <v>4.201295614242554</v>
+        <v>4.241472721099854</v>
       </c>
       <c r="I29" t="n">
-        <v>4.648655652999878</v>
+        <v>4.373116493225098</v>
       </c>
       <c r="J29" t="n">
-        <v>4.977793216705322</v>
+        <v>4.970077514648438</v>
       </c>
       <c r="K29" t="n">
-        <v>4.959357261657715</v>
+        <v>4.443437337875366</v>
       </c>
       <c r="L29" t="n">
-        <v>4.678324484825135</v>
+        <v>4.554380583763122</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>4.506030321121216</v>
+        <v>4.247933387756348</v>
       </c>
       <c r="C30" t="n">
-        <v>4.226208925247192</v>
+        <v>5.18052077293396</v>
       </c>
       <c r="D30" t="n">
-        <v>3.923492908477783</v>
+        <v>4.059597015380859</v>
       </c>
       <c r="E30" t="n">
-        <v>3.925483703613281</v>
+        <v>4.902090549468994</v>
       </c>
       <c r="F30" t="n">
-        <v>4.647651672363281</v>
+        <v>3.836210250854492</v>
       </c>
       <c r="G30" t="n">
-        <v>3.869117498397827</v>
+        <v>4.53544807434082</v>
       </c>
       <c r="H30" t="n">
-        <v>3.928996562957764</v>
+        <v>4.89651083946228</v>
       </c>
       <c r="I30" t="n">
-        <v>4.504504680633545</v>
+        <v>4.405778884887695</v>
       </c>
       <c r="J30" t="n">
-        <v>4.302535533905029</v>
+        <v>4.212268352508545</v>
       </c>
       <c r="K30" t="n">
-        <v>4.842146873474121</v>
+        <v>4.895018815994263</v>
       </c>
       <c r="L30" t="n">
-        <v>4.267616868019104</v>
+        <v>4.517137694358826</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>5.059090375900269</v>
+        <v>4.940414428710938</v>
       </c>
       <c r="C31" t="n">
-        <v>5.212698936462402</v>
+        <v>4.718460083007812</v>
       </c>
       <c r="D31" t="n">
-        <v>5.288997650146484</v>
+        <v>4.828684091567993</v>
       </c>
       <c r="E31" t="n">
-        <v>5.36635160446167</v>
+        <v>4.797749280929565</v>
       </c>
       <c r="F31" t="n">
-        <v>4.868583917617798</v>
+        <v>5.12445068359375</v>
       </c>
       <c r="G31" t="n">
-        <v>4.581318140029907</v>
+        <v>5.201789855957031</v>
       </c>
       <c r="H31" t="n">
-        <v>5.460078001022339</v>
+        <v>4.490089654922485</v>
       </c>
       <c r="I31" t="n">
-        <v>4.81273627281189</v>
+        <v>4.861576318740845</v>
       </c>
       <c r="J31" t="n">
-        <v>4.698529720306396</v>
+        <v>4.606255769729614</v>
       </c>
       <c r="K31" t="n">
-        <v>5.103484869003296</v>
+        <v>5.071569204330444</v>
       </c>
       <c r="L31" t="n">
-        <v>5.045186948776245</v>
+        <v>4.864103937149048</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>5.193763017654419</v>
+        <v>4.472131729125977</v>
       </c>
       <c r="C32" t="n">
-        <v>5.489493846893311</v>
+        <v>4.935904026031494</v>
       </c>
       <c r="D32" t="n">
-        <v>5.06209659576416</v>
+        <v>5.222657203674316</v>
       </c>
       <c r="E32" t="n">
-        <v>4.673587083816528</v>
+        <v>4.919957160949707</v>
       </c>
       <c r="F32" t="n">
-        <v>6.974494218826294</v>
+        <v>5.245630264282227</v>
       </c>
       <c r="G32" t="n">
-        <v>5.427448987960815</v>
+        <v>5.050678491592407</v>
       </c>
       <c r="H32" t="n">
-        <v>4.779814958572388</v>
+        <v>4.74541187286377</v>
       </c>
       <c r="I32" t="n">
-        <v>5.211696863174438</v>
+        <v>5.100512981414795</v>
       </c>
       <c r="J32" t="n">
-        <v>4.873660802841187</v>
+        <v>4.696575164794922</v>
       </c>
       <c r="K32" t="n">
-        <v>4.804726362228394</v>
+        <v>4.796559810638428</v>
       </c>
       <c r="L32" t="n">
-        <v>5.249078273773193</v>
+        <v>4.918601870536804</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>5.035656929016113</v>
+        <v>4.900725126266479</v>
       </c>
       <c r="C33" t="n">
-        <v>5.100001096725464</v>
+        <v>4.67383599281311</v>
       </c>
       <c r="D33" t="n">
-        <v>4.957351684570312</v>
+        <v>4.528206348419189</v>
       </c>
       <c r="E33" t="n">
-        <v>4.480062007904053</v>
+        <v>4.547655820846558</v>
       </c>
       <c r="F33" t="n">
-        <v>4.494539737701416</v>
+        <v>5.105206966400146</v>
       </c>
       <c r="G33" t="n">
-        <v>4.977295160293579</v>
+        <v>5.140114068984985</v>
       </c>
       <c r="H33" t="n">
-        <v>5.382288455963135</v>
+        <v>5.438330888748169</v>
       </c>
       <c r="I33" t="n">
-        <v>4.503012895584106</v>
+        <v>5.116201877593994</v>
       </c>
       <c r="J33" t="n">
-        <v>4.813879251480103</v>
+        <v>4.48235297203064</v>
       </c>
       <c r="K33" t="n">
-        <v>4.877292394638062</v>
+        <v>4.34268593788147</v>
       </c>
       <c r="L33" t="n">
-        <v>4.862137961387634</v>
+        <v>4.827531599998474</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>4.47784161567688</v>
+        <v>4.263926982879639</v>
       </c>
       <c r="C34" t="n">
-        <v>3.998582124710083</v>
+        <v>4.108157396316528</v>
       </c>
       <c r="D34" t="n">
-        <v>4.464876651763916</v>
+        <v>4.523968458175659</v>
       </c>
       <c r="E34" t="n">
-        <v>4.380086898803711</v>
+        <v>4.278581142425537</v>
       </c>
       <c r="F34" t="n">
-        <v>4.375611543655396</v>
+        <v>4.511994361877441</v>
       </c>
       <c r="G34" t="n">
-        <v>4.434445142745972</v>
+        <v>4.353898763656616</v>
       </c>
       <c r="H34" t="n">
-        <v>4.037478923797607</v>
+        <v>3.943448781967163</v>
       </c>
       <c r="I34" t="n">
-        <v>3.894388198852539</v>
+        <v>4.464610576629639</v>
       </c>
       <c r="J34" t="n">
-        <v>4.090837955474854</v>
+        <v>4.319499492645264</v>
       </c>
       <c r="K34" t="n">
-        <v>4.529688596725464</v>
+        <v>5.100677490234375</v>
       </c>
       <c r="L34" t="n">
-        <v>4.268383765220642</v>
+        <v>4.386876344680786</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>4.356145858764648</v>
+        <v>3.747947931289673</v>
       </c>
       <c r="C35" t="n">
-        <v>3.7058424949646</v>
+        <v>3.637730121612549</v>
       </c>
       <c r="D35" t="n">
-        <v>4.06639552116394</v>
+        <v>3.872622966766357</v>
       </c>
       <c r="E35" t="n">
-        <v>3.781144618988037</v>
+        <v>3.599807500839233</v>
       </c>
       <c r="F35" t="n">
-        <v>3.945718288421631</v>
+        <v>3.893584012985229</v>
       </c>
       <c r="G35" t="n">
-        <v>3.884871959686279</v>
+        <v>4.020755290985107</v>
       </c>
       <c r="H35" t="n">
-        <v>3.618589401245117</v>
+        <v>3.633529186248779</v>
       </c>
       <c r="I35" t="n">
-        <v>3.956738471984863</v>
+        <v>3.76721715927124</v>
       </c>
       <c r="J35" t="n">
-        <v>3.704846620559692</v>
+        <v>3.724796295166016</v>
       </c>
       <c r="K35" t="n">
-        <v>4.604006052017212</v>
+        <v>3.72978138923645</v>
       </c>
       <c r="L35" t="n">
-        <v>3.962429928779602</v>
+        <v>3.762777185440064</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>4.390582323074341</v>
+        <v>4.938629388809204</v>
       </c>
       <c r="C36" t="n">
-        <v>5.005943536758423</v>
+        <v>4.593037128448486</v>
       </c>
       <c r="D36" t="n">
-        <v>4.351167917251587</v>
+        <v>4.352702140808105</v>
       </c>
       <c r="E36" t="n">
-        <v>4.220999002456665</v>
+        <v>5.481719732284546</v>
       </c>
       <c r="F36" t="n">
-        <v>4.813460111618042</v>
+        <v>4.363645792007446</v>
       </c>
       <c r="G36" t="n">
-        <v>4.550525665283203</v>
+        <v>4.832417488098145</v>
       </c>
       <c r="H36" t="n">
-        <v>5.587233781814575</v>
+        <v>4.850892543792725</v>
       </c>
       <c r="I36" t="n">
-        <v>5.245126008987427</v>
+        <v>4.580564737319946</v>
       </c>
       <c r="J36" t="n">
-        <v>5.053092956542969</v>
+        <v>4.549186944961548</v>
       </c>
       <c r="K36" t="n">
-        <v>4.253178834915161</v>
+        <v>4.247933387756348</v>
       </c>
       <c r="L36" t="n">
-        <v>4.74713101387024</v>
+        <v>4.67907292842865</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>4.970804452896118</v>
+        <v>5.207499504089355</v>
       </c>
       <c r="C37" t="n">
-        <v>5.398236989974976</v>
+        <v>4.92266583442688</v>
       </c>
       <c r="D37" t="n">
-        <v>5.55732274055481</v>
+        <v>4.728179454803467</v>
       </c>
       <c r="E37" t="n">
-        <v>5.312972545623779</v>
+        <v>5.459304332733154</v>
       </c>
       <c r="F37" t="n">
-        <v>5.647090911865234</v>
+        <v>5.301692008972168</v>
       </c>
       <c r="G37" t="n">
-        <v>5.522397994995117</v>
+        <v>5.545066118240356</v>
       </c>
       <c r="H37" t="n">
-        <v>5.501198053359985</v>
+        <v>5.184507608413696</v>
       </c>
       <c r="I37" t="n">
-        <v>5.576960563659668</v>
+        <v>5.516151428222656</v>
       </c>
       <c r="J37" t="n">
-        <v>4.967055559158325</v>
+        <v>5.096240043640137</v>
       </c>
       <c r="K37" t="n">
-        <v>5.321637392044067</v>
+        <v>5.138146162033081</v>
       </c>
       <c r="L37" t="n">
-        <v>5.377567720413208</v>
+        <v>5.209945249557495</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>4.25544548034668</v>
+        <v>4.156208992004395</v>
       </c>
       <c r="C38" t="n">
-        <v>4.152684926986694</v>
+        <v>3.806106090545654</v>
       </c>
       <c r="D38" t="n">
-        <v>4.26937460899353</v>
+        <v>4.236023426055908</v>
       </c>
       <c r="E38" t="n">
-        <v>4.149812698364258</v>
+        <v>5.089262008666992</v>
       </c>
       <c r="F38" t="n">
-        <v>4.412765026092529</v>
+        <v>3.854958534240723</v>
       </c>
       <c r="G38" t="n">
-        <v>4.308585643768311</v>
+        <v>4.697274684906006</v>
       </c>
       <c r="H38" t="n">
-        <v>5.093504190444946</v>
+        <v>3.970685482025146</v>
       </c>
       <c r="I38" t="n">
-        <v>4.040683746337891</v>
+        <v>4.18609094619751</v>
       </c>
       <c r="J38" t="n">
-        <v>4.424716711044312</v>
+        <v>4.143712759017944</v>
       </c>
       <c r="K38" t="n">
-        <v>4.914989709854126</v>
+        <v>3.785140991210938</v>
       </c>
       <c r="L38" t="n">
-        <v>4.402256274223328</v>
+        <v>4.192546391487122</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>4.259633779525757</v>
+        <v>4.574582815170288</v>
       </c>
       <c r="C39" t="n">
-        <v>4.518999576568604</v>
+        <v>4.16863751411438</v>
       </c>
       <c r="D39" t="n">
-        <v>4.643177270889282</v>
+        <v>4.773564577102661</v>
       </c>
       <c r="E39" t="n">
-        <v>4.746895790100098</v>
+        <v>4.202068567276001</v>
       </c>
       <c r="F39" t="n">
-        <v>4.001781463623047</v>
+        <v>4.545670032501221</v>
       </c>
       <c r="G39" t="n">
-        <v>4.15388822555542</v>
+        <v>4.158181428909302</v>
       </c>
       <c r="H39" t="n">
-        <v>4.572330713272095</v>
+        <v>3.919288635253906</v>
       </c>
       <c r="I39" t="n">
-        <v>4.555862665176392</v>
+        <v>4.123756885528564</v>
       </c>
       <c r="J39" t="n">
-        <v>4.136932134628296</v>
+        <v>4.293987989425659</v>
       </c>
       <c r="K39" t="n">
-        <v>4.583326578140259</v>
+        <v>4.295048713684082</v>
       </c>
       <c r="L39" t="n">
-        <v>4.417282819747925</v>
+        <v>4.305478715896607</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>4.29752779006958</v>
+        <v>4.337437868118286</v>
       </c>
       <c r="C40" t="n">
-        <v>4.316498756408691</v>
+        <v>4.516981601715088</v>
       </c>
       <c r="D40" t="n">
-        <v>5.401242256164551</v>
+        <v>4.750393867492676</v>
       </c>
       <c r="E40" t="n">
-        <v>5.347395420074463</v>
+        <v>4.605271816253662</v>
       </c>
       <c r="F40" t="n">
-        <v>5.336892366409302</v>
+        <v>4.405768871307373</v>
       </c>
       <c r="G40" t="n">
-        <v>4.949870824813843</v>
+        <v>4.813752412796021</v>
       </c>
       <c r="H40" t="n">
-        <v>4.473083019256592</v>
+        <v>5.041653633117676</v>
       </c>
       <c r="I40" t="n">
-        <v>4.880588531494141</v>
+        <v>4.788320302963257</v>
       </c>
       <c r="J40" t="n">
-        <v>4.718962907791138</v>
+        <v>4.581319093704224</v>
       </c>
       <c r="K40" t="n">
-        <v>4.642149686813354</v>
+        <v>5.175809144973755</v>
       </c>
       <c r="L40" t="n">
-        <v>4.836421155929566</v>
+        <v>4.701670861244201</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>4.790786027908325</v>
+        <v>4.344429492950439</v>
       </c>
       <c r="C41" t="n">
-        <v>4.201289892196655</v>
+        <v>4.581353902816772</v>
       </c>
       <c r="D41" t="n">
-        <v>4.797252416610718</v>
+        <v>4.224222183227539</v>
       </c>
       <c r="E41" t="n">
-        <v>4.548396825790405</v>
+        <v>3.87662410736084</v>
       </c>
       <c r="F41" t="n">
-        <v>4.106063604354858</v>
+        <v>4.352401256561279</v>
       </c>
       <c r="G41" t="n">
-        <v>5.016234397888184</v>
+        <v>4.339951515197754</v>
       </c>
       <c r="H41" t="n">
-        <v>4.227199554443359</v>
+        <v>4.278108596801758</v>
       </c>
       <c r="I41" t="n">
-        <v>4.626192808151245</v>
+        <v>4.760890245437622</v>
       </c>
       <c r="J41" t="n">
-        <v>4.471122026443481</v>
+        <v>4.163074016571045</v>
       </c>
       <c r="K41" t="n">
-        <v>4.647153377532959</v>
+        <v>4.133463144302368</v>
       </c>
       <c r="L41" t="n">
-        <v>4.543169093132019</v>
+        <v>4.305451846122741</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>4.982285737991333</v>
+        <v>5.179275989532471</v>
       </c>
       <c r="C42" t="n">
-        <v>5.716967582702637</v>
+        <v>4.666606187820435</v>
       </c>
       <c r="D42" t="n">
-        <v>5.171831846237183</v>
+        <v>5.343942880630493</v>
       </c>
       <c r="E42" t="n">
-        <v>5.138396263122559</v>
+        <v>4.902740478515625</v>
       </c>
       <c r="F42" t="n">
-        <v>4.773838758468628</v>
+        <v>5.572094917297363</v>
       </c>
       <c r="G42" t="n">
-        <v>5.275558710098267</v>
+        <v>5.119178533554077</v>
       </c>
       <c r="H42" t="n">
-        <v>4.954379558563232</v>
+        <v>5.163044214248657</v>
       </c>
       <c r="I42" t="n">
-        <v>5.709965705871582</v>
+        <v>5.441328287124634</v>
       </c>
       <c r="J42" t="n">
-        <v>5.263581991195679</v>
+        <v>5.612390041351318</v>
       </c>
       <c r="K42" t="n">
-        <v>4.718472719192505</v>
+        <v>5.378497838973999</v>
       </c>
       <c r="L42" t="n">
-        <v>5.170527887344361</v>
+        <v>5.237909936904908</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>4.867118835449219</v>
+        <v>4.611027002334595</v>
       </c>
       <c r="C43" t="n">
-        <v>5.204743623733521</v>
+        <v>5.402946949005127</v>
       </c>
       <c r="D43" t="n">
-        <v>4.668090581893921</v>
+        <v>4.884798049926758</v>
       </c>
       <c r="E43" t="n">
-        <v>4.935418367385864</v>
+        <v>4.616243600845337</v>
       </c>
       <c r="F43" t="n">
-        <v>5.51543140411377</v>
+        <v>5.663068532943726</v>
       </c>
       <c r="G43" t="n">
-        <v>5.227664470672607</v>
+        <v>4.341420412063599</v>
       </c>
       <c r="H43" t="n">
-        <v>4.764320611953735</v>
+        <v>5.823721170425415</v>
       </c>
       <c r="I43" t="n">
-        <v>5.309967041015625</v>
+        <v>5.409214973449707</v>
       </c>
       <c r="J43" t="n">
-        <v>5.450605869293213</v>
+        <v>5.001239538192749</v>
       </c>
       <c r="K43" t="n">
-        <v>5.24266242980957</v>
+        <v>4.78781533241272</v>
       </c>
       <c r="L43" t="n">
-        <v>5.118602323532104</v>
+        <v>5.054149556159973</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>4.13695216178894</v>
+        <v>4.851625680923462</v>
       </c>
       <c r="C44" t="n">
-        <v>4.343939542770386</v>
+        <v>5.169826030731201</v>
       </c>
       <c r="D44" t="n">
-        <v>4.42969536781311</v>
+        <v>4.551133871078491</v>
       </c>
       <c r="E44" t="n">
-        <v>4.820732593536377</v>
+        <v>4.597034454345703</v>
       </c>
       <c r="F44" t="n">
-        <v>4.498042345046997</v>
+        <v>4.894749402999878</v>
       </c>
       <c r="G44" t="n">
-        <v>5.029175281524658</v>
+        <v>4.493061542510986</v>
       </c>
       <c r="H44" t="n">
-        <v>4.836180925369263</v>
+        <v>4.607245445251465</v>
       </c>
       <c r="I44" t="n">
-        <v>4.268615961074829</v>
+        <v>4.439671754837036</v>
       </c>
       <c r="J44" t="n">
-        <v>5.267568111419678</v>
+        <v>5.137392044067383</v>
       </c>
       <c r="K44" t="n">
-        <v>4.871065855026245</v>
+        <v>4.554425239562988</v>
       </c>
       <c r="L44" t="n">
-        <v>4.650196814537049</v>
+        <v>4.72961654663086</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>3.965886354446411</v>
+        <v>4.201283931732178</v>
       </c>
       <c r="C45" t="n">
-        <v>4.389277696609497</v>
+        <v>4.519986629486084</v>
       </c>
       <c r="D45" t="n">
-        <v>4.576363563537598</v>
+        <v>4.597296237945557</v>
       </c>
       <c r="E45" t="n">
-        <v>5.00823187828064</v>
+        <v>4.346414804458618</v>
       </c>
       <c r="F45" t="n">
-        <v>4.723441600799561</v>
+        <v>4.694532632827759</v>
       </c>
       <c r="G45" t="n">
-        <v>4.317475557327271</v>
+        <v>4.717493057250977</v>
       </c>
       <c r="H45" t="n">
-        <v>4.450285196304321</v>
+        <v>4.146452188491821</v>
       </c>
       <c r="I45" t="n">
-        <v>4.337717056274414</v>
+        <v>4.565864324569702</v>
       </c>
       <c r="J45" t="n">
-        <v>4.539671897888184</v>
+        <v>4.004782915115356</v>
       </c>
       <c r="K45" t="n">
-        <v>4.065915584564209</v>
+        <v>4.589312791824341</v>
       </c>
       <c r="L45" t="n">
-        <v>4.437426638603211</v>
+        <v>4.438341951370239</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>4.375121831893921</v>
+        <v>4.280588150024414</v>
       </c>
       <c r="C46" t="n">
-        <v>4.406513452529907</v>
+        <v>4.62720513343811</v>
       </c>
       <c r="D46" t="n">
-        <v>4.522724151611328</v>
+        <v>4.272147417068481</v>
       </c>
       <c r="E46" t="n">
-        <v>4.611976385116577</v>
+        <v>4.502295970916748</v>
       </c>
       <c r="F46" t="n">
-        <v>4.761616945266724</v>
+        <v>4.490806341171265</v>
       </c>
       <c r="G46" t="n">
-        <v>4.4678635597229</v>
+        <v>4.380602359771729</v>
       </c>
       <c r="H46" t="n">
-        <v>4.574837446212769</v>
+        <v>4.031495332717896</v>
       </c>
       <c r="I46" t="n">
-        <v>4.62920093536377</v>
+        <v>4.278359174728394</v>
       </c>
       <c r="J46" t="n">
-        <v>4.499014139175415</v>
+        <v>4.596754789352417</v>
       </c>
       <c r="K46" t="n">
-        <v>4.113004684448242</v>
+        <v>4.158665895462036</v>
       </c>
       <c r="L46" t="n">
-        <v>4.496187353134156</v>
+        <v>4.361892056465149</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>4.081095218658447</v>
+        <v>4.31128978729248</v>
       </c>
       <c r="C47" t="n">
-        <v>3.813276529312134</v>
+        <v>4.62895393371582</v>
       </c>
       <c r="D47" t="n">
-        <v>4.645659923553467</v>
+        <v>4.097820043563843</v>
       </c>
       <c r="E47" t="n">
-        <v>3.766894578933716</v>
+        <v>3.901341676712036</v>
       </c>
       <c r="F47" t="n">
-        <v>4.055164098739624</v>
+        <v>3.972143411636353</v>
       </c>
       <c r="G47" t="n">
-        <v>4.427713394165039</v>
+        <v>4.20105242729187</v>
       </c>
       <c r="H47" t="n">
-        <v>4.544900178909302</v>
+        <v>4.216029644012451</v>
       </c>
       <c r="I47" t="n">
-        <v>4.434703826904297</v>
+        <v>3.691898584365845</v>
       </c>
       <c r="J47" t="n">
-        <v>4.5603928565979</v>
+        <v>4.525719165802002</v>
       </c>
       <c r="K47" t="n">
-        <v>5.309980392456055</v>
+        <v>4.065922260284424</v>
       </c>
       <c r="L47" t="n">
-        <v>4.363978099822998</v>
+        <v>4.161217093467712</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>4.974322080612183</v>
+        <v>5.182561874389648</v>
       </c>
       <c r="C48" t="n">
-        <v>5.19127345085144</v>
+        <v>5.051838874816895</v>
       </c>
       <c r="D48" t="n">
-        <v>4.898998975753784</v>
+        <v>5.101244688034058</v>
       </c>
       <c r="E48" t="n">
-        <v>4.779809474945068</v>
+        <v>4.842386960983276</v>
       </c>
       <c r="F48" t="n">
-        <v>4.872080087661743</v>
+        <v>5.633539199829102</v>
       </c>
       <c r="G48" t="n">
-        <v>4.898479700088501</v>
+        <v>4.67909836769104</v>
       </c>
       <c r="H48" t="n">
-        <v>4.965339422225952</v>
+        <v>5.165835618972778</v>
       </c>
       <c r="I48" t="n">
-        <v>4.717474699020386</v>
+        <v>5.226692199707031</v>
       </c>
       <c r="J48" t="n">
-        <v>4.82867956161499</v>
+        <v>5.260576009750366</v>
       </c>
       <c r="K48" t="n">
-        <v>5.149881362915039</v>
+        <v>4.778839588165283</v>
       </c>
       <c r="L48" t="n">
-        <v>4.927633881568909</v>
+        <v>5.092261338233948</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>4.902987480163574</v>
+        <v>4.543975114822388</v>
       </c>
       <c r="C49" t="n">
-        <v>4.487582445144653</v>
+        <v>4.573358774185181</v>
       </c>
       <c r="D49" t="n">
-        <v>5.012225151062012</v>
+        <v>5.732858896255493</v>
       </c>
       <c r="E49" t="n">
-        <v>4.706480264663696</v>
+        <v>4.910994052886963</v>
       </c>
       <c r="F49" t="n">
-        <v>4.580334663391113</v>
+        <v>4.781815052032471</v>
       </c>
       <c r="G49" t="n">
-        <v>4.864102363586426</v>
+        <v>5.090523719787598</v>
       </c>
       <c r="H49" t="n">
-        <v>5.001236200332642</v>
+        <v>4.707515001296997</v>
       </c>
       <c r="I49" t="n">
-        <v>4.429717302322388</v>
+        <v>4.769330739974976</v>
       </c>
       <c r="J49" t="n">
-        <v>4.864593029022217</v>
+        <v>4.943880796432495</v>
       </c>
       <c r="K49" t="n">
-        <v>4.70948338508606</v>
+        <v>5.033693313598633</v>
       </c>
       <c r="L49" t="n">
-        <v>4.755874228477478</v>
+        <v>4.90879454612732</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>4.673569202423096</v>
+        <v>4.233217000961304</v>
       </c>
       <c r="C50" t="n">
-        <v>4.517971992492676</v>
+        <v>4.310588598251343</v>
       </c>
       <c r="D50" t="n">
-        <v>4.247185945510864</v>
+        <v>4.205286264419556</v>
       </c>
       <c r="E50" t="n">
-        <v>4.519477844238281</v>
+        <v>4.967379093170166</v>
       </c>
       <c r="F50" t="n">
-        <v>4.665117740631104</v>
+        <v>4.152947902679443</v>
       </c>
       <c r="G50" t="n">
-        <v>4.021732807159424</v>
+        <v>4.107012271881104</v>
       </c>
       <c r="H50" t="n">
-        <v>3.633731603622437</v>
+        <v>4.264634132385254</v>
       </c>
       <c r="I50" t="n">
-        <v>4.577322483062744</v>
+        <v>4.034713745117188</v>
       </c>
       <c r="J50" t="n">
-        <v>4.247181177139282</v>
+        <v>4.000801801681519</v>
       </c>
       <c r="K50" t="n">
-        <v>5.02777361869812</v>
+        <v>3.868647813796997</v>
       </c>
       <c r="L50" t="n">
-        <v>4.413106441497803</v>
+        <v>4.214522862434388</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>5.047139644622803</v>
+        <v>4.426739692687988</v>
       </c>
       <c r="C51" t="n">
-        <v>4.872107267379761</v>
+        <v>4.947866201400757</v>
       </c>
       <c r="D51" t="n">
-        <v>4.996286153793335</v>
+        <v>4.592284917831421</v>
       </c>
       <c r="E51" t="n">
-        <v>4.566902875900269</v>
+        <v>4.601291656494141</v>
       </c>
       <c r="F51" t="n">
-        <v>5.2890305519104</v>
+        <v>4.269622802734375</v>
       </c>
       <c r="G51" t="n">
-        <v>4.60241174697876</v>
+        <v>4.275084495544434</v>
       </c>
       <c r="H51" t="n">
-        <v>5.376806497573853</v>
+        <v>4.554382562637329</v>
       </c>
       <c r="I51" t="n">
-        <v>5.819727897644043</v>
+        <v>4.057660579681396</v>
       </c>
       <c r="J51" t="n">
-        <v>4.765354871749878</v>
+        <v>4.110015392303467</v>
       </c>
       <c r="K51" t="n">
-        <v>4.828711986541748</v>
+        <v>4.381824016571045</v>
       </c>
       <c r="L51" t="n">
-        <v>5.016447949409485</v>
+        <v>4.421677231788635</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4.559674897193909</v>
+        <v>4.644751124382019</v>
       </c>
       <c r="C52" t="n">
-        <v>4.613612928390503</v>
+        <v>4.581734251976013</v>
       </c>
       <c r="D52" t="n">
-        <v>4.634741473197937</v>
+        <v>4.609728741645813</v>
       </c>
       <c r="E52" t="n">
-        <v>4.60024091720581</v>
+        <v>4.589959883689881</v>
       </c>
       <c r="F52" t="n">
-        <v>4.714616355895996</v>
+        <v>4.631865811347962</v>
       </c>
       <c r="G52" t="n">
-        <v>4.653448362350463</v>
+        <v>4.632120761871338</v>
       </c>
       <c r="H52" t="n">
-        <v>4.634408140182495</v>
+        <v>4.542507920265198</v>
       </c>
       <c r="I52" t="n">
-        <v>4.646592721939087</v>
+        <v>4.678731212615967</v>
       </c>
       <c r="J52" t="n">
-        <v>4.643861160278321</v>
+        <v>4.531917357444764</v>
       </c>
       <c r="K52" t="n">
-        <v>4.700294914245606</v>
+        <v>4.585121445655822</v>
       </c>
       <c r="L52" t="n">
-        <v>4.640149187088013</v>
+        <v>4.602843851089478</v>
       </c>
     </row>
   </sheetData>
